--- a/research/traditional_assets/database/data/thailand/thailand_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_semiconductor.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1528248349793369</v>
+        <v>0.1525551853093782</v>
       </c>
       <c r="C2">
-        <v>59.3621853273903</v>
+        <v>58.91045774315408</v>
       </c>
       <c r="D2">
-        <v>57.6721853273903</v>
+        <v>57.81785774315409</v>
       </c>
       <c r="E2">
-        <v>-4.04</v>
+        <v>-3.4426</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5974</v>
       </c>
       <c r="G2">
         <v>1.69</v>
@@ -1579,28 +1579,28 @@
         <v>3.52</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03004922</v>
       </c>
       <c r="N2">
-        <v>3.52</v>
+        <v>3.48995078</v>
       </c>
       <c r="O2">
-        <v>0.7040000000000001</v>
+        <v>0.697990156</v>
       </c>
       <c r="P2">
-        <v>2.816</v>
+        <v>2.791960624</v>
       </c>
       <c r="Q2">
-        <v>2.476</v>
+        <v>2.451960624</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1528248349793369</v>
+        <v>0.153689682130685</v>
       </c>
       <c r="T2">
-        <v>1.655640159154051</v>
+        <v>1.669019069531054</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>117.1411437634654</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1525551853093782</v>
+        <v>0.1522855356394195</v>
       </c>
       <c r="C3">
-        <v>58.91045774315408</v>
+        <v>58.45946792144301</v>
       </c>
       <c r="D3">
-        <v>57.81785774315409</v>
+        <v>57.96426792144302</v>
       </c>
       <c r="E3">
-        <v>-3.4426</v>
+        <v>-2.8452</v>
       </c>
       <c r="F3">
-        <v>0.5974</v>
+        <v>1.1948</v>
       </c>
       <c r="G3">
         <v>1.69</v>
@@ -1661,28 +1661,28 @@
         <v>3.52</v>
       </c>
       <c r="M3">
-        <v>0.03004922</v>
+        <v>0.06009844</v>
       </c>
       <c r="N3">
-        <v>3.48995078</v>
+        <v>3.45990156</v>
       </c>
       <c r="O3">
-        <v>0.697990156</v>
+        <v>0.6919803120000001</v>
       </c>
       <c r="P3">
-        <v>2.791960624</v>
+        <v>2.767921248</v>
       </c>
       <c r="Q3">
-        <v>2.451960624</v>
+        <v>2.427921248</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.153689682130685</v>
+        <v>0.1545721792238974</v>
       </c>
       <c r="T3">
-        <v>1.669019069531054</v>
+        <v>1.682671018895342</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>117.1411437634654</v>
+        <v>58.5705718817327</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1522855356394195</v>
+        <v>0.1520158859694608</v>
       </c>
       <c r="C4">
-        <v>58.45946792144301</v>
+        <v>58.00922148111776</v>
       </c>
       <c r="D4">
-        <v>57.96426792144302</v>
+        <v>58.11142148111777</v>
       </c>
       <c r="E4">
-        <v>-2.8452</v>
+        <v>-2.2478</v>
       </c>
       <c r="F4">
-        <v>1.1948</v>
+        <v>1.7922</v>
       </c>
       <c r="G4">
         <v>1.69</v>
@@ -1743,28 +1743,28 @@
         <v>3.52</v>
       </c>
       <c r="M4">
-        <v>0.06009844</v>
+        <v>0.09014765999999999</v>
       </c>
       <c r="N4">
-        <v>3.45990156</v>
+        <v>3.42985234</v>
       </c>
       <c r="O4">
-        <v>0.6919803120000001</v>
+        <v>0.6859704680000001</v>
       </c>
       <c r="P4">
-        <v>2.767921248</v>
+        <v>2.743881872</v>
       </c>
       <c r="Q4">
-        <v>2.427921248</v>
+        <v>2.403881872</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1545721792238974</v>
+        <v>0.1554728721334648</v>
       </c>
       <c r="T4">
-        <v>1.682671018895342</v>
+        <v>1.696604451751677</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.5705718817327</v>
+        <v>39.04704792115514</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1520158859694608</v>
+        <v>0.1517462362995022</v>
       </c>
       <c r="C5">
-        <v>58.00922148111776</v>
+        <v>57.5597240982425</v>
       </c>
       <c r="D5">
-        <v>58.11142148111777</v>
+        <v>58.2593240982425</v>
       </c>
       <c r="E5">
-        <v>-2.2478</v>
+        <v>-1.6504</v>
       </c>
       <c r="F5">
-        <v>1.7922</v>
+        <v>2.3896</v>
       </c>
       <c r="G5">
         <v>1.69</v>
@@ -1825,28 +1825,28 @@
         <v>3.52</v>
       </c>
       <c r="M5">
-        <v>0.09014765999999999</v>
+        <v>0.12019688</v>
       </c>
       <c r="N5">
-        <v>3.42985234</v>
+        <v>3.39980312</v>
       </c>
       <c r="O5">
-        <v>0.6859704680000001</v>
+        <v>0.679960624</v>
       </c>
       <c r="P5">
-        <v>2.743881872</v>
+        <v>2.719842496</v>
       </c>
       <c r="Q5">
-        <v>2.403881872</v>
+        <v>2.379842496</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1554728721334648</v>
+        <v>0.1563923294786481</v>
       </c>
       <c r="T5">
-        <v>1.696604451751677</v>
+        <v>1.710828164459187</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.04704792115514</v>
+        <v>29.28528594086635</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1517462362995022</v>
+        <v>0.1514765866295434</v>
       </c>
       <c r="C6">
-        <v>57.5597240982425</v>
+        <v>57.11098150681474</v>
       </c>
       <c r="D6">
-        <v>58.2593240982425</v>
+        <v>58.40798150681474</v>
       </c>
       <c r="E6">
-        <v>-1.6504</v>
+        <v>-1.053</v>
       </c>
       <c r="F6">
-        <v>2.3896</v>
+        <v>2.987</v>
       </c>
       <c r="G6">
         <v>1.69</v>
@@ -1907,28 +1907,28 @@
         <v>3.52</v>
       </c>
       <c r="M6">
-        <v>0.12019688</v>
+        <v>0.1502461</v>
       </c>
       <c r="N6">
-        <v>3.39980312</v>
+        <v>3.3697539</v>
       </c>
       <c r="O6">
-        <v>0.679960624</v>
+        <v>0.6739507800000001</v>
       </c>
       <c r="P6">
-        <v>2.719842496</v>
+        <v>2.69580312</v>
       </c>
       <c r="Q6">
-        <v>2.379842496</v>
+        <v>2.35580312</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1563923294786481</v>
+        <v>0.1573311438205721</v>
       </c>
       <c r="T6">
-        <v>1.710828164459187</v>
+        <v>1.725351323750011</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.28528594086635</v>
+        <v>23.42822875269308</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1514765866295434</v>
+        <v>0.1512069369595848</v>
       </c>
       <c r="C7">
-        <v>57.11098150681474</v>
+        <v>56.66299949950625</v>
       </c>
       <c r="D7">
-        <v>58.40798150681474</v>
+        <v>58.55739949950625</v>
       </c>
       <c r="E7">
-        <v>-1.053</v>
+        <v>-0.4555999999999996</v>
       </c>
       <c r="F7">
-        <v>2.987</v>
+        <v>3.5844</v>
       </c>
       <c r="G7">
         <v>1.69</v>
@@ -1989,28 +1989,28 @@
         <v>3.52</v>
       </c>
       <c r="M7">
-        <v>0.1502461</v>
+        <v>0.18029532</v>
       </c>
       <c r="N7">
-        <v>3.3697539</v>
+        <v>3.33970468</v>
       </c>
       <c r="O7">
-        <v>0.6739507800000001</v>
+        <v>0.667940936</v>
       </c>
       <c r="P7">
-        <v>2.69580312</v>
+        <v>2.671763744</v>
       </c>
       <c r="Q7">
-        <v>2.35580312</v>
+        <v>2.331763744</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1573311438205721</v>
+        <v>0.1582899329357285</v>
       </c>
       <c r="T7">
-        <v>1.725351323750011</v>
+        <v>1.740183486430003</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.42822875269308</v>
+        <v>19.52352396057757</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1512069369595848</v>
+        <v>0.1509372872896261</v>
       </c>
       <c r="C8">
-        <v>56.66299949950625</v>
+        <v>56.2157839284157</v>
       </c>
       <c r="D8">
-        <v>58.55739949950625</v>
+        <v>58.70758392841571</v>
       </c>
       <c r="E8">
-        <v>-0.4556</v>
+        <v>0.1417999999999999</v>
       </c>
       <c r="F8">
-        <v>3.5844</v>
+        <v>4.1818</v>
       </c>
       <c r="G8">
         <v>1.69</v>
@@ -2071,28 +2071,28 @@
         <v>3.52</v>
       </c>
       <c r="M8">
-        <v>0.18029532</v>
+        <v>0.21034454</v>
       </c>
       <c r="N8">
-        <v>3.33970468</v>
+        <v>3.30965546</v>
       </c>
       <c r="O8">
-        <v>0.667940936</v>
+        <v>0.6619310920000001</v>
       </c>
       <c r="P8">
-        <v>2.671763744</v>
+        <v>2.647724368</v>
       </c>
       <c r="Q8">
-        <v>2.331763744</v>
+        <v>2.307724368</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1582899329357285</v>
+        <v>0.159269341171641</v>
       </c>
       <c r="T8">
-        <v>1.740183486430003</v>
+        <v>1.755334620350425</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.52352396057757</v>
+        <v>16.73444910906649</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1509372872896261</v>
+        <v>0.1506676376196674</v>
       </c>
       <c r="C9">
-        <v>56.21578392841572</v>
+        <v>55.76934070583242</v>
       </c>
       <c r="D9">
-        <v>58.70758392841572</v>
+        <v>58.85854070583243</v>
       </c>
       <c r="E9">
-        <v>0.1418000000000008</v>
+        <v>0.7392000000000003</v>
       </c>
       <c r="F9">
-        <v>4.181800000000001</v>
+        <v>4.7792</v>
       </c>
       <c r="G9">
         <v>1.69</v>
@@ -2153,28 +2153,28 @@
         <v>3.52</v>
       </c>
       <c r="M9">
-        <v>0.21034454</v>
+        <v>0.24039376</v>
       </c>
       <c r="N9">
-        <v>3.30965546</v>
+        <v>3.27960624</v>
       </c>
       <c r="O9">
-        <v>0.6619310920000001</v>
+        <v>0.6559212480000001</v>
       </c>
       <c r="P9">
-        <v>2.647724368</v>
+        <v>2.623684992</v>
       </c>
       <c r="Q9">
-        <v>2.307724368</v>
+        <v>2.283684992</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.159269341171641</v>
+        <v>0.1602700408909429</v>
       </c>
       <c r="T9">
-        <v>1.755334620350425</v>
+        <v>1.770815126747377</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.73444910906649</v>
+        <v>14.64264297043318</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1506676376196674</v>
+        <v>0.1503979879497088</v>
       </c>
       <c r="C10">
-        <v>55.76934070583242</v>
+        <v>55.3236758050124</v>
       </c>
       <c r="D10">
-        <v>58.85854070583243</v>
+        <v>59.01027580501241</v>
       </c>
       <c r="E10">
-        <v>0.7392000000000003</v>
+        <v>1.3366</v>
       </c>
       <c r="F10">
-        <v>4.7792</v>
+        <v>5.3766</v>
       </c>
       <c r="G10">
         <v>1.69</v>
@@ -2235,28 +2235,28 @@
         <v>3.52</v>
       </c>
       <c r="M10">
-        <v>0.24039376</v>
+        <v>0.27044298</v>
       </c>
       <c r="N10">
-        <v>3.27960624</v>
+        <v>3.24955702</v>
       </c>
       <c r="O10">
-        <v>0.6559212480000001</v>
+        <v>0.649911404</v>
       </c>
       <c r="P10">
-        <v>2.623684992</v>
+        <v>2.599645616</v>
       </c>
       <c r="Q10">
-        <v>2.283684992</v>
+        <v>2.259645616</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1602700408909429</v>
+        <v>0.161292734010669</v>
       </c>
       <c r="T10">
-        <v>1.770815126747377</v>
+        <v>1.786635864054152</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.64264297043318</v>
+        <v>13.01568264038505</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1503979879497088</v>
+        <v>0.1502483382797501</v>
       </c>
       <c r="C11">
-        <v>55.3236758050124</v>
+        <v>54.81082351964181</v>
       </c>
       <c r="D11">
-        <v>59.01027580501241</v>
+        <v>59.09482351964181</v>
       </c>
       <c r="E11">
-        <v>1.3366</v>
+        <v>1.933999999999999</v>
       </c>
       <c r="F11">
-        <v>5.3766</v>
+        <v>5.973999999999999</v>
       </c>
       <c r="G11">
         <v>1.69</v>
@@ -2317,45 +2317,45 @@
         <v>3.52</v>
       </c>
       <c r="M11">
-        <v>0.27044298</v>
+        <v>0.3094532</v>
       </c>
       <c r="N11">
-        <v>3.24955702</v>
+        <v>3.2105468</v>
       </c>
       <c r="O11">
-        <v>0.649911404</v>
+        <v>0.6421093600000001</v>
       </c>
       <c r="P11">
-        <v>2.599645616</v>
+        <v>2.56843744</v>
       </c>
       <c r="Q11">
-        <v>2.259645616</v>
+        <v>2.22843744</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.161292734010669</v>
+        <v>0.1623381536441668</v>
       </c>
       <c r="T11">
-        <v>1.786635864054152</v>
+        <v>1.802808173301078</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.01568264038505</v>
+        <v>11.37490257008168</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1502483382797501</v>
+        <v>0.1499906886097914</v>
       </c>
       <c r="C12">
-        <v>54.81082351964179</v>
+        <v>54.35955713272431</v>
       </c>
       <c r="D12">
-        <v>59.09482351964179</v>
+        <v>59.2409571327243</v>
       </c>
       <c r="E12">
-        <v>1.934</v>
+        <v>2.531400000000001</v>
       </c>
       <c r="F12">
-        <v>5.974</v>
+        <v>6.571400000000001</v>
       </c>
       <c r="G12">
         <v>1.69</v>
@@ -2399,28 +2399,28 @@
         <v>3.52</v>
       </c>
       <c r="M12">
-        <v>0.3094532</v>
+        <v>0.34039852</v>
       </c>
       <c r="N12">
-        <v>3.2105468</v>
+        <v>3.17960148</v>
       </c>
       <c r="O12">
-        <v>0.6421093600000001</v>
+        <v>0.6359202960000001</v>
       </c>
       <c r="P12">
-        <v>2.56843744</v>
+        <v>2.543681184</v>
       </c>
       <c r="Q12">
-        <v>2.22843744</v>
+        <v>2.203681184</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1623381536441668</v>
+        <v>0.1634070658536982</v>
       </c>
       <c r="T12">
-        <v>1.802808173301079</v>
+        <v>1.819343905227711</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.37490257008168</v>
+        <v>10.34082051825607</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1499906886097914</v>
+        <v>0.1498962389398328</v>
       </c>
       <c r="C13">
-        <v>54.35955713272431</v>
+        <v>53.81590824713733</v>
       </c>
       <c r="D13">
-        <v>59.2409571327243</v>
+        <v>59.29470824713733</v>
       </c>
       <c r="E13">
-        <v>2.531400000000001</v>
+        <v>3.1288</v>
       </c>
       <c r="F13">
-        <v>6.571400000000001</v>
+        <v>7.1688</v>
       </c>
       <c r="G13">
         <v>1.69</v>
@@ -2481,45 +2481,45 @@
         <v>3.52</v>
       </c>
       <c r="M13">
-        <v>0.34039852</v>
+        <v>0.3835308</v>
       </c>
       <c r="N13">
-        <v>3.17960148</v>
+        <v>3.1364692</v>
       </c>
       <c r="O13">
-        <v>0.6359202960000001</v>
+        <v>0.6272938400000001</v>
       </c>
       <c r="P13">
-        <v>2.543681184</v>
+        <v>2.50917536</v>
       </c>
       <c r="Q13">
-        <v>2.203681184</v>
+        <v>2.16917536</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1634070658536982</v>
+        <v>0.1645002715225372</v>
       </c>
       <c r="T13">
-        <v>1.819343905227711</v>
+        <v>1.836255449243585</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.34082051825607</v>
+        <v>9.177880889878988</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1498962389398328</v>
+        <v>0.1496521892698741</v>
       </c>
       <c r="C14">
-        <v>53.81590824713733</v>
+        <v>53.35784911303283</v>
       </c>
       <c r="D14">
-        <v>59.29470824713733</v>
+        <v>59.43404911303283</v>
       </c>
       <c r="E14">
-        <v>3.1288</v>
+        <v>3.7262</v>
       </c>
       <c r="F14">
-        <v>7.1688</v>
+        <v>7.7662</v>
       </c>
       <c r="G14">
         <v>1.69</v>
@@ -2563,28 +2563,28 @@
         <v>3.52</v>
       </c>
       <c r="M14">
-        <v>0.3835308</v>
+        <v>0.4154917</v>
       </c>
       <c r="N14">
-        <v>3.1364692</v>
+        <v>3.1045083</v>
       </c>
       <c r="O14">
-        <v>0.6272938400000001</v>
+        <v>0.62090166</v>
       </c>
       <c r="P14">
-        <v>2.50917536</v>
+        <v>2.48360664</v>
       </c>
       <c r="Q14">
-        <v>2.16917536</v>
+        <v>2.14360664</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1645002715225372</v>
+        <v>0.1656186083561771</v>
       </c>
       <c r="T14">
-        <v>1.836255449243585</v>
+        <v>1.85355576438626</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.177880889878988</v>
+        <v>8.471890052195988</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1496521892698741</v>
+        <v>0.1494081395999154</v>
       </c>
       <c r="C15">
-        <v>53.35784911303283</v>
+        <v>52.90044641562271</v>
       </c>
       <c r="D15">
-        <v>59.43404911303283</v>
+        <v>59.57404641562272</v>
       </c>
       <c r="E15">
-        <v>3.7262</v>
+        <v>4.323600000000002</v>
       </c>
       <c r="F15">
-        <v>7.7662</v>
+        <v>8.363600000000002</v>
       </c>
       <c r="G15">
         <v>1.69</v>
@@ -2645,28 +2645,28 @@
         <v>3.52</v>
       </c>
       <c r="M15">
-        <v>0.4154917</v>
+        <v>0.4474526000000001</v>
       </c>
       <c r="N15">
-        <v>3.1045083</v>
+        <v>3.0725474</v>
       </c>
       <c r="O15">
-        <v>0.62090166</v>
+        <v>0.6145094800000001</v>
       </c>
       <c r="P15">
-        <v>2.48360664</v>
+        <v>2.45803792</v>
       </c>
       <c r="Q15">
-        <v>2.14360664</v>
+        <v>2.11803792</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1656186083561771</v>
+        <v>0.1667629530231575</v>
       </c>
       <c r="T15">
-        <v>1.85355576438626</v>
+        <v>1.87125841243923</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.471890052195988</v>
+        <v>7.866755048467702</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1494081395999154</v>
+        <v>0.1492600899299567</v>
       </c>
       <c r="C16">
-        <v>52.90044641562271</v>
+        <v>52.38829588636943</v>
       </c>
       <c r="D16">
-        <v>59.57404641562272</v>
+        <v>59.65929588636943</v>
       </c>
       <c r="E16">
-        <v>4.323600000000002</v>
+        <v>4.921000000000002</v>
       </c>
       <c r="F16">
-        <v>8.363600000000002</v>
+        <v>8.961000000000002</v>
       </c>
       <c r="G16">
         <v>1.69</v>
@@ -2727,45 +2727,45 @@
         <v>3.52</v>
       </c>
       <c r="M16">
-        <v>0.4474526000000001</v>
+        <v>0.4865823000000001</v>
       </c>
       <c r="N16">
-        <v>3.0725474</v>
+        <v>3.0334177</v>
       </c>
       <c r="O16">
-        <v>0.6145094800000001</v>
+        <v>0.60668354</v>
       </c>
       <c r="P16">
-        <v>2.45803792</v>
+        <v>2.42673416</v>
       </c>
       <c r="Q16">
-        <v>2.11803792</v>
+        <v>2.08673416</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1667629530231575</v>
+        <v>0.1679342234470079</v>
       </c>
       <c r="T16">
-        <v>1.87125841243923</v>
+        <v>1.889377593387565</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.866755048467702</v>
+        <v>7.234130793495774</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1492600899299567</v>
+        <v>0.149022440259998</v>
       </c>
       <c r="C17">
-        <v>52.38829588636943</v>
+        <v>51.92824985651055</v>
       </c>
       <c r="D17">
-        <v>59.65929588636943</v>
+        <v>59.79664985651056</v>
       </c>
       <c r="E17">
-        <v>4.921</v>
+        <v>5.518400000000001</v>
       </c>
       <c r="F17">
-        <v>8.961</v>
+        <v>9.558400000000001</v>
       </c>
       <c r="G17">
         <v>1.69</v>
@@ -2809,28 +2809,28 @@
         <v>3.52</v>
       </c>
       <c r="M17">
-        <v>0.4865823</v>
+        <v>0.51902112</v>
       </c>
       <c r="N17">
-        <v>3.0334177</v>
+        <v>3.00097888</v>
       </c>
       <c r="O17">
-        <v>0.6066835400000001</v>
+        <v>0.6001957760000001</v>
       </c>
       <c r="P17">
-        <v>2.42673416</v>
+        <v>2.400783104</v>
       </c>
       <c r="Q17">
-        <v>2.08673416</v>
+        <v>2.060783104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1679342234470079</v>
+        <v>0.1691333812619024</v>
       </c>
       <c r="T17">
-        <v>1.889377593387565</v>
+        <v>1.907928183406097</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.234130793495777</v>
+        <v>6.78199761890229</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.149022440259998</v>
+        <v>0.1487847905900394</v>
       </c>
       <c r="C18">
-        <v>51.92824985651055</v>
+        <v>51.46883774794204</v>
       </c>
       <c r="D18">
-        <v>59.79664985651056</v>
+        <v>59.93463774794204</v>
       </c>
       <c r="E18">
-        <v>5.518400000000001</v>
+        <v>6.115800000000001</v>
       </c>
       <c r="F18">
-        <v>9.558400000000001</v>
+        <v>10.1558</v>
       </c>
       <c r="G18">
         <v>1.69</v>
@@ -2891,28 +2891,28 @@
         <v>3.52</v>
       </c>
       <c r="M18">
-        <v>0.51902112</v>
+        <v>0.5514599400000001</v>
       </c>
       <c r="N18">
-        <v>3.00097888</v>
+        <v>2.96854006</v>
       </c>
       <c r="O18">
-        <v>0.6001957760000001</v>
+        <v>0.593708012</v>
       </c>
       <c r="P18">
-        <v>2.400783104</v>
+        <v>2.374832048</v>
       </c>
       <c r="Q18">
-        <v>2.060783104</v>
+        <v>2.034832048</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1691333812619024</v>
+        <v>0.1703614344458306</v>
       </c>
       <c r="T18">
-        <v>1.907928183406097</v>
+        <v>1.926925775593751</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.78199761890229</v>
+        <v>6.383056582496272</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1487847905900394</v>
+        <v>0.1486911409200807</v>
       </c>
       <c r="C19">
-        <v>51.46883774794204</v>
+        <v>50.92598917962015</v>
       </c>
       <c r="D19">
-        <v>59.93463774794204</v>
+        <v>59.98918917962015</v>
       </c>
       <c r="E19">
-        <v>6.115800000000001</v>
+        <v>6.713200000000001</v>
       </c>
       <c r="F19">
-        <v>10.1558</v>
+        <v>10.7532</v>
       </c>
       <c r="G19">
         <v>1.69</v>
@@ -2973,45 +2973,45 @@
         <v>3.52</v>
       </c>
       <c r="M19">
-        <v>0.5514599400000001</v>
+        <v>0.5946519600000001</v>
       </c>
       <c r="N19">
-        <v>2.96854006</v>
+        <v>2.92534804</v>
       </c>
       <c r="O19">
-        <v>0.593708012</v>
+        <v>0.585069608</v>
       </c>
       <c r="P19">
-        <v>2.374832048</v>
+        <v>2.340278432</v>
       </c>
       <c r="Q19">
-        <v>2.034832048</v>
+        <v>2.000278432</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1703614344458306</v>
+        <v>0.1716194401464399</v>
       </c>
       <c r="T19">
-        <v>1.926925775593751</v>
+        <v>1.946386723688422</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.383056582496272</v>
+        <v>5.919428904261914</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1486911409200807</v>
+        <v>0.1484614912501221</v>
       </c>
       <c r="C20">
-        <v>50.92598917962015</v>
+        <v>50.46278260822157</v>
       </c>
       <c r="D20">
-        <v>59.98918917962015</v>
+        <v>60.12338260822158</v>
       </c>
       <c r="E20">
-        <v>6.7132</v>
+        <v>7.3106</v>
       </c>
       <c r="F20">
-        <v>10.7532</v>
+        <v>11.3506</v>
       </c>
       <c r="G20">
         <v>1.69</v>
@@ -3055,28 +3055,28 @@
         <v>3.52</v>
       </c>
       <c r="M20">
-        <v>0.59465196</v>
+        <v>0.62768818</v>
       </c>
       <c r="N20">
-        <v>2.92534804</v>
+        <v>2.89231182</v>
       </c>
       <c r="O20">
-        <v>0.5850696080000001</v>
+        <v>0.578462364</v>
       </c>
       <c r="P20">
-        <v>2.340278432</v>
+        <v>2.313849456</v>
       </c>
       <c r="Q20">
-        <v>2.000278432</v>
+        <v>1.973849456</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1716194401464399</v>
+        <v>0.1729085077162001</v>
       </c>
       <c r="T20">
-        <v>1.946386723688421</v>
+        <v>1.966328189019997</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.919428904261915</v>
+        <v>5.607880014563919</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1484614912501221</v>
+        <v>0.1482318415801634</v>
       </c>
       <c r="C21">
-        <v>50.46278260822157</v>
+        <v>50.00017775355705</v>
       </c>
       <c r="D21">
-        <v>60.12338260822158</v>
+        <v>60.25817775355705</v>
       </c>
       <c r="E21">
-        <v>7.3106</v>
+        <v>7.908</v>
       </c>
       <c r="F21">
-        <v>11.3506</v>
+        <v>11.948</v>
       </c>
       <c r="G21">
         <v>1.69</v>
@@ -3137,28 +3137,28 @@
         <v>3.52</v>
       </c>
       <c r="M21">
-        <v>0.62768818</v>
+        <v>0.6607244000000001</v>
       </c>
       <c r="N21">
-        <v>2.89231182</v>
+        <v>2.8592756</v>
       </c>
       <c r="O21">
-        <v>0.578462364</v>
+        <v>0.5718551200000001</v>
       </c>
       <c r="P21">
-        <v>2.313849456</v>
+        <v>2.28742048</v>
       </c>
       <c r="Q21">
-        <v>1.973849456</v>
+        <v>1.94742048</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1729085077162001</v>
+        <v>0.1742298019752042</v>
       </c>
       <c r="T21">
-        <v>1.966328189019997</v>
+        <v>1.986768190984862</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.607880014563919</v>
+        <v>5.327486013835723</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1482318415801634</v>
+        <v>0.1480021919102047</v>
       </c>
       <c r="C22">
-        <v>50.00017775355705</v>
+        <v>49.53817867182281</v>
       </c>
       <c r="D22">
-        <v>60.25817775355705</v>
+        <v>60.39357867182282</v>
       </c>
       <c r="E22">
-        <v>7.908</v>
+        <v>8.505400000000002</v>
       </c>
       <c r="F22">
-        <v>11.948</v>
+        <v>12.5454</v>
       </c>
       <c r="G22">
         <v>1.69</v>
@@ -3219,28 +3219,28 @@
         <v>3.52</v>
       </c>
       <c r="M22">
-        <v>0.6607244000000001</v>
+        <v>0.6937606200000001</v>
       </c>
       <c r="N22">
-        <v>2.8592756</v>
+        <v>2.82623938</v>
       </c>
       <c r="O22">
-        <v>0.5718551200000001</v>
+        <v>0.565247876</v>
       </c>
       <c r="P22">
-        <v>2.28742048</v>
+        <v>2.260991504</v>
       </c>
       <c r="Q22">
-        <v>1.94742048</v>
+        <v>1.920991504</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1742298019752042</v>
+        <v>0.1755845467217781</v>
       </c>
       <c r="T22">
-        <v>1.986768190984862</v>
+        <v>2.0077256613539</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.327486013835723</v>
+        <v>5.073796203653069</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1480021919102047</v>
+        <v>0.1477725422402461</v>
       </c>
       <c r="C23">
-        <v>49.53817867182281</v>
+        <v>49.07678945575452</v>
       </c>
       <c r="D23">
-        <v>60.39357867182282</v>
+        <v>60.52958945575453</v>
       </c>
       <c r="E23">
-        <v>8.505400000000002</v>
+        <v>9.102800000000002</v>
       </c>
       <c r="F23">
-        <v>12.5454</v>
+        <v>13.1428</v>
       </c>
       <c r="G23">
         <v>1.69</v>
@@ -3301,28 +3301,28 @@
         <v>3.52</v>
       </c>
       <c r="M23">
-        <v>0.6937606200000001</v>
+        <v>0.7267968400000001</v>
       </c>
       <c r="N23">
-        <v>2.82623938</v>
+        <v>2.79320316</v>
       </c>
       <c r="O23">
-        <v>0.565247876</v>
+        <v>0.558640632</v>
       </c>
       <c r="P23">
-        <v>2.260991504</v>
+        <v>2.234562528</v>
       </c>
       <c r="Q23">
-        <v>1.920991504</v>
+        <v>1.894562528</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1755845467217781</v>
+        <v>0.1769740285131359</v>
       </c>
       <c r="T23">
-        <v>2.0077256613539</v>
+        <v>2.029220502758043</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.073796203653069</v>
+        <v>4.843169103487021</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1477725422402461</v>
+        <v>0.1475428925702874</v>
       </c>
       <c r="C24">
-        <v>49.07678945575452</v>
+        <v>48.61601423503969</v>
       </c>
       <c r="D24">
-        <v>60.52958945575453</v>
+        <v>60.66621423503969</v>
       </c>
       <c r="E24">
-        <v>9.102800000000002</v>
+        <v>9.700200000000002</v>
       </c>
       <c r="F24">
-        <v>13.1428</v>
+        <v>13.7402</v>
       </c>
       <c r="G24">
         <v>1.69</v>
@@ -3383,28 +3383,28 @@
         <v>3.52</v>
       </c>
       <c r="M24">
-        <v>0.7267968400000001</v>
+        <v>0.7598330600000001</v>
       </c>
       <c r="N24">
-        <v>2.79320316</v>
+        <v>2.76016694</v>
       </c>
       <c r="O24">
-        <v>0.558640632</v>
+        <v>0.552033388</v>
       </c>
       <c r="P24">
-        <v>2.234562528</v>
+        <v>2.208133552</v>
       </c>
       <c r="Q24">
-        <v>1.894562528</v>
+        <v>1.868133552</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1769740285131359</v>
+        <v>0.1783996007406329</v>
       </c>
       <c r="T24">
-        <v>2.029220502758043</v>
+        <v>2.051273651731124</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.843169103487021</v>
+        <v>4.632596533770194</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1475428925702874</v>
+        <v>0.1477932429003287</v>
       </c>
       <c r="C25">
-        <v>48.61601423503969</v>
+        <v>47.86970430410491</v>
       </c>
       <c r="D25">
-        <v>60.66621423503969</v>
+        <v>60.51730430410492</v>
       </c>
       <c r="E25">
-        <v>9.700200000000002</v>
+        <v>10.2976</v>
       </c>
       <c r="F25">
-        <v>13.7402</v>
+        <v>14.3376</v>
       </c>
       <c r="G25">
         <v>1.69</v>
@@ -3465,45 +3465,45 @@
         <v>3.52</v>
       </c>
       <c r="M25">
-        <v>0.7598330600000001</v>
+        <v>0.8287132800000002</v>
       </c>
       <c r="N25">
-        <v>2.76016694</v>
+        <v>2.69128672</v>
       </c>
       <c r="O25">
-        <v>0.552033388</v>
+        <v>0.538257344</v>
       </c>
       <c r="P25">
-        <v>2.208133552</v>
+        <v>2.153029376</v>
       </c>
       <c r="Q25">
-        <v>1.868133552</v>
+        <v>1.813029376</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1783996007406329</v>
+        <v>0.1798626880267483</v>
       </c>
       <c r="T25">
-        <v>2.051273651731124</v>
+        <v>2.073907146729812</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.632596533770194</v>
+        <v>4.247548681734651</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1477932429003287</v>
+        <v>0.14758359323037</v>
       </c>
       <c r="C26">
-        <v>47.86970430410493</v>
+        <v>47.39695536496331</v>
       </c>
       <c r="D26">
-        <v>60.51730430410493</v>
+        <v>60.64195536496332</v>
       </c>
       <c r="E26">
-        <v>10.2976</v>
+        <v>10.895</v>
       </c>
       <c r="F26">
-        <v>14.3376</v>
+        <v>14.935</v>
       </c>
       <c r="G26">
         <v>1.69</v>
@@ -3547,28 +3547,28 @@
         <v>3.52</v>
       </c>
       <c r="M26">
-        <v>0.8287132800000001</v>
+        <v>0.8632430000000001</v>
       </c>
       <c r="N26">
-        <v>2.69128672</v>
+        <v>2.656757</v>
       </c>
       <c r="O26">
-        <v>0.538257344</v>
+        <v>0.5313514</v>
       </c>
       <c r="P26">
-        <v>2.153029376</v>
+        <v>2.1254056</v>
       </c>
       <c r="Q26">
-        <v>1.813029376</v>
+        <v>1.7854056</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1798626880267482</v>
+        <v>0.1813647909738267</v>
       </c>
       <c r="T26">
-        <v>2.073907146729812</v>
+        <v>2.097144201595132</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.247548681734652</v>
+        <v>4.077646734465266</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.14758359323037</v>
+        <v>0.1481019435604113</v>
       </c>
       <c r="C27">
-        <v>47.39695536496331</v>
+        <v>46.49229064951615</v>
       </c>
       <c r="D27">
-        <v>60.64195536496332</v>
+        <v>60.33469064951615</v>
       </c>
       <c r="E27">
-        <v>10.895</v>
+        <v>11.4924</v>
       </c>
       <c r="F27">
-        <v>14.935</v>
+        <v>15.5324</v>
       </c>
       <c r="G27">
         <v>1.69</v>
@@ -3629,45 +3629,45 @@
         <v>3.52</v>
       </c>
       <c r="M27">
-        <v>0.8632430000000001</v>
+        <v>0.95213612</v>
       </c>
       <c r="N27">
-        <v>2.656757</v>
+        <v>2.56786388</v>
       </c>
       <c r="O27">
-        <v>0.5313514</v>
+        <v>0.5135727760000001</v>
       </c>
       <c r="P27">
-        <v>2.1254056</v>
+        <v>2.054291104</v>
       </c>
       <c r="Q27">
-        <v>1.7854056</v>
+        <v>1.714291104</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1813647909738267</v>
+        <v>0.1829074912978532</v>
       </c>
       <c r="T27">
-        <v>2.097144201595132</v>
+        <v>2.121009284970325</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.077646734465266</v>
+        <v>3.696950389824514</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1481019435604113</v>
+        <v>0.1479202938904527</v>
       </c>
       <c r="C28">
-        <v>46.49229064951615</v>
+        <v>46.00221286947863</v>
       </c>
       <c r="D28">
-        <v>60.33469064951615</v>
+        <v>60.44201286947863</v>
       </c>
       <c r="E28">
-        <v>11.4924</v>
+        <v>12.0898</v>
       </c>
       <c r="F28">
-        <v>15.5324</v>
+        <v>16.1298</v>
       </c>
       <c r="G28">
         <v>1.69</v>
@@ -3711,28 +3711,28 @@
         <v>3.52</v>
       </c>
       <c r="M28">
-        <v>0.95213612</v>
+        <v>0.9887567400000002</v>
       </c>
       <c r="N28">
-        <v>2.56786388</v>
+        <v>2.53124326</v>
       </c>
       <c r="O28">
-        <v>0.5135727760000001</v>
+        <v>0.5062486519999999</v>
       </c>
       <c r="P28">
-        <v>2.054291104</v>
+        <v>2.024994608</v>
       </c>
       <c r="Q28">
-        <v>1.714291104</v>
+        <v>1.684994608</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1829074912978532</v>
+        <v>0.1844924573841817</v>
       </c>
       <c r="T28">
-        <v>2.121009284970325</v>
+        <v>2.14552820624621</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.696950389824514</v>
+        <v>3.560026301312494</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1479202938904527</v>
+        <v>0.148365844220494</v>
       </c>
       <c r="C29">
-        <v>46.00221286947863</v>
+        <v>45.14225022996615</v>
       </c>
       <c r="D29">
-        <v>60.44201286947863</v>
+        <v>60.17945022996616</v>
       </c>
       <c r="E29">
-        <v>12.0898</v>
+        <v>12.6872</v>
       </c>
       <c r="F29">
-        <v>16.1298</v>
+        <v>16.7272</v>
       </c>
       <c r="G29">
         <v>1.69</v>
@@ -3793,45 +3793,45 @@
         <v>3.52</v>
       </c>
       <c r="M29">
-        <v>0.9887567400000002</v>
+        <v>1.07221352</v>
       </c>
       <c r="N29">
-        <v>2.53124326</v>
+        <v>2.44778648</v>
       </c>
       <c r="O29">
-        <v>0.5062486519999999</v>
+        <v>0.4895572959999999</v>
       </c>
       <c r="P29">
-        <v>2.024994608</v>
+        <v>1.958229184</v>
       </c>
       <c r="Q29">
-        <v>1.684994608</v>
+        <v>1.618229184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1844924573841817</v>
+        <v>0.1861214503062417</v>
       </c>
       <c r="T29">
-        <v>2.14552820624621</v>
+        <v>2.170728208668645</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.560026301312494</v>
+        <v>3.282928198853526</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.148365844220494</v>
+        <v>0.1482065945505353</v>
       </c>
       <c r="C30">
-        <v>45.14225022996615</v>
+        <v>44.63843363276828</v>
       </c>
       <c r="D30">
-        <v>60.17945022996616</v>
+        <v>60.27303363276829</v>
       </c>
       <c r="E30">
-        <v>12.6872</v>
+        <v>13.2846</v>
       </c>
       <c r="F30">
-        <v>16.7272</v>
+        <v>17.3246</v>
       </c>
       <c r="G30">
         <v>1.69</v>
@@ -3875,28 +3875,28 @@
         <v>3.52</v>
       </c>
       <c r="M30">
-        <v>1.07221352</v>
+        <v>1.11050686</v>
       </c>
       <c r="N30">
-        <v>2.44778648</v>
+        <v>2.409493139999999</v>
       </c>
       <c r="O30">
-        <v>0.4895572959999999</v>
+        <v>0.4818986279999999</v>
       </c>
       <c r="P30">
-        <v>1.958229184</v>
+        <v>1.927594512</v>
       </c>
       <c r="Q30">
-        <v>1.618229184</v>
+        <v>1.587594512</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1861214503062417</v>
+        <v>0.1877963303528666</v>
       </c>
       <c r="T30">
-        <v>2.170728208668645</v>
+        <v>2.196638070314249</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.282928198853526</v>
+        <v>3.169723778203404</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1482065945505353</v>
+        <v>0.1480473448805766</v>
       </c>
       <c r="C31">
-        <v>44.63843363276828</v>
+        <v>44.13490854682729</v>
       </c>
       <c r="D31">
-        <v>60.27303363276829</v>
+        <v>60.36690854682729</v>
       </c>
       <c r="E31">
-        <v>13.2846</v>
+        <v>13.882</v>
       </c>
       <c r="F31">
-        <v>17.3246</v>
+        <v>17.922</v>
       </c>
       <c r="G31">
         <v>1.69</v>
@@ -3957,28 +3957,28 @@
         <v>3.52</v>
       </c>
       <c r="M31">
-        <v>1.11050686</v>
+        <v>1.1488002</v>
       </c>
       <c r="N31">
-        <v>2.40949314</v>
+        <v>2.3711998</v>
       </c>
       <c r="O31">
-        <v>0.481898628</v>
+        <v>0.47423996</v>
       </c>
       <c r="P31">
-        <v>1.927594512</v>
+        <v>1.89695984</v>
       </c>
       <c r="Q31">
-        <v>1.587594512</v>
+        <v>1.55695984</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1877963303528666</v>
+        <v>0.1895190641151095</v>
       </c>
       <c r="T31">
-        <v>2.196638070314249</v>
+        <v>2.223288213721155</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.169723778203405</v>
+        <v>3.064066318929958</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1480473448805766</v>
+        <v>0.1498224952106179</v>
       </c>
       <c r="C32">
-        <v>44.13490854682729</v>
+        <v>42.5073435097985</v>
       </c>
       <c r="D32">
-        <v>60.36690854682729</v>
+        <v>59.3367435097985</v>
       </c>
       <c r="E32">
-        <v>13.882</v>
+        <v>14.4794</v>
       </c>
       <c r="F32">
-        <v>17.922</v>
+        <v>18.5194</v>
       </c>
       <c r="G32">
         <v>1.69</v>
@@ -4039,45 +4039,45 @@
         <v>3.52</v>
       </c>
       <c r="M32">
-        <v>1.1488002</v>
+        <v>1.33154486</v>
       </c>
       <c r="N32">
-        <v>2.3711998</v>
+        <v>2.18845514</v>
       </c>
       <c r="O32">
-        <v>0.47423996</v>
+        <v>0.437691028</v>
       </c>
       <c r="P32">
-        <v>1.89695984</v>
+        <v>1.750764112</v>
       </c>
       <c r="Q32">
-        <v>1.55695984</v>
+        <v>1.410764112</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1895190641151095</v>
+        <v>0.1912917321893014</v>
       </c>
       <c r="T32">
-        <v>2.223288213721155</v>
+        <v>2.250710825052899</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.064066318929958</v>
+        <v>2.643545933555704</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1498224952106179</v>
+        <v>0.1497256455406593</v>
       </c>
       <c r="C33">
-        <v>42.5073435097985</v>
+        <v>41.96524019807453</v>
       </c>
       <c r="D33">
-        <v>59.3367435097985</v>
+        <v>59.39204019807453</v>
       </c>
       <c r="E33">
-        <v>14.4794</v>
+        <v>15.0768</v>
       </c>
       <c r="F33">
-        <v>18.5194</v>
+        <v>19.1168</v>
       </c>
       <c r="G33">
         <v>1.69</v>
@@ -4121,28 +4121,28 @@
         <v>3.52</v>
       </c>
       <c r="M33">
-        <v>1.33154486</v>
+        <v>1.37449792</v>
       </c>
       <c r="N33">
-        <v>2.18845514</v>
+        <v>2.14550208</v>
       </c>
       <c r="O33">
-        <v>0.437691028</v>
+        <v>0.429100416</v>
       </c>
       <c r="P33">
-        <v>1.750764112</v>
+        <v>1.716401664</v>
       </c>
       <c r="Q33">
-        <v>1.410764112</v>
+        <v>1.376401664</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1912917321893014</v>
+        <v>0.1931165375597931</v>
       </c>
       <c r="T33">
-        <v>2.250710825052899</v>
+        <v>2.278939983776753</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.643545933555704</v>
+        <v>2.560935123132088</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1497256455406593</v>
+        <v>0.1506583958707006</v>
       </c>
       <c r="C34">
-        <v>41.96524019807453</v>
+        <v>40.83952823376704</v>
       </c>
       <c r="D34">
-        <v>59.39204019807453</v>
+        <v>58.86372823376704</v>
       </c>
       <c r="E34">
-        <v>15.0768</v>
+        <v>15.6742</v>
       </c>
       <c r="F34">
-        <v>19.1168</v>
+        <v>19.7142</v>
       </c>
       <c r="G34">
         <v>1.69</v>
@@ -4203,45 +4203,45 @@
         <v>3.52</v>
       </c>
       <c r="M34">
-        <v>1.37449792</v>
+        <v>1.49433636</v>
       </c>
       <c r="N34">
-        <v>2.14550208</v>
+        <v>2.025663639999999</v>
       </c>
       <c r="O34">
-        <v>0.429100416</v>
+        <v>0.4051327279999999</v>
       </c>
       <c r="P34">
-        <v>1.716401664</v>
+        <v>1.620530912</v>
       </c>
       <c r="Q34">
-        <v>1.376401664</v>
+        <v>1.280530912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1931165375597931</v>
+        <v>0.194995814732389</v>
       </c>
       <c r="T34">
-        <v>2.278939983776753</v>
+        <v>2.308011803955051</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.560935123132088</v>
+        <v>2.355560698529747</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1506583958707006</v>
+        <v>0.1505927462007419</v>
       </c>
       <c r="C35">
-        <v>40.83952823376704</v>
+        <v>40.27900468248308</v>
       </c>
       <c r="D35">
-        <v>58.86372823376704</v>
+        <v>58.90060468248308</v>
       </c>
       <c r="E35">
-        <v>15.6742</v>
+        <v>16.2716</v>
       </c>
       <c r="F35">
-        <v>19.7142</v>
+        <v>20.3116</v>
       </c>
       <c r="G35">
         <v>1.69</v>
@@ -4285,28 +4285,28 @@
         <v>3.52</v>
       </c>
       <c r="M35">
-        <v>1.49433636</v>
+        <v>1.53961928</v>
       </c>
       <c r="N35">
-        <v>2.025663639999999</v>
+        <v>1.98038072</v>
       </c>
       <c r="O35">
-        <v>0.4051327279999999</v>
+        <v>0.396076144</v>
       </c>
       <c r="P35">
-        <v>1.620530912</v>
+        <v>1.584304576</v>
       </c>
       <c r="Q35">
-        <v>1.280530912</v>
+        <v>1.244304576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.194995814732389</v>
+        <v>0.1969320396980938</v>
       </c>
       <c r="T35">
-        <v>2.308011803955051</v>
+        <v>2.337964588381176</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.355560698529747</v>
+        <v>2.286279501514166</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1505927462007419</v>
+        <v>0.1505270965307832</v>
       </c>
       <c r="C36">
-        <v>40.27900468248308</v>
+        <v>39.71852736425181</v>
       </c>
       <c r="D36">
-        <v>58.90060468248308</v>
+        <v>58.93752736425181</v>
       </c>
       <c r="E36">
-        <v>16.2716</v>
+        <v>16.869</v>
       </c>
       <c r="F36">
-        <v>20.3116</v>
+        <v>20.909</v>
       </c>
       <c r="G36">
         <v>1.69</v>
@@ -4367,28 +4367,28 @@
         <v>3.52</v>
       </c>
       <c r="M36">
-        <v>1.53961928</v>
+        <v>1.5849022</v>
       </c>
       <c r="N36">
-        <v>1.98038072</v>
+        <v>1.9350978</v>
       </c>
       <c r="O36">
-        <v>0.396076144</v>
+        <v>0.3870195599999999</v>
       </c>
       <c r="P36">
-        <v>1.584304576</v>
+        <v>1.54807824</v>
       </c>
       <c r="Q36">
-        <v>1.244304576</v>
+        <v>1.20807824</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1969320396980938</v>
+        <v>0.1989278408165897</v>
       </c>
       <c r="T36">
-        <v>2.337964588381176</v>
+        <v>2.368838996943489</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.286279501514166</v>
+        <v>2.220957230042333</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1505270965307832</v>
+        <v>0.1504614468608246</v>
       </c>
       <c r="C37">
-        <v>39.71852736425181</v>
+        <v>39.15809636607335</v>
       </c>
       <c r="D37">
-        <v>58.93752736425181</v>
+        <v>58.97449636607335</v>
       </c>
       <c r="E37">
-        <v>16.869</v>
+        <v>17.4664</v>
       </c>
       <c r="F37">
-        <v>20.909</v>
+        <v>21.5064</v>
       </c>
       <c r="G37">
         <v>1.69</v>
@@ -4449,28 +4449,28 @@
         <v>3.52</v>
       </c>
       <c r="M37">
-        <v>1.5849022</v>
+        <v>1.63018512</v>
       </c>
       <c r="N37">
-        <v>1.9350978</v>
+        <v>1.88981488</v>
       </c>
       <c r="O37">
-        <v>0.3870195599999999</v>
+        <v>0.377962976</v>
       </c>
       <c r="P37">
-        <v>1.54807824</v>
+        <v>1.511851904</v>
       </c>
       <c r="Q37">
-        <v>1.20807824</v>
+        <v>1.171851904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1989278408165897</v>
+        <v>0.2009860107200385</v>
       </c>
       <c r="T37">
-        <v>2.368838996943489</v>
+        <v>2.400678230773375</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.220957230042333</v>
+        <v>2.159263973652268</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1504614468608246</v>
+        <v>0.1503957971908659</v>
       </c>
       <c r="C38">
-        <v>39.15809636607335</v>
+        <v>38.5977117751662</v>
       </c>
       <c r="D38">
-        <v>58.97449636607335</v>
+        <v>59.0115117751662</v>
       </c>
       <c r="E38">
-        <v>17.4664</v>
+        <v>18.0638</v>
       </c>
       <c r="F38">
-        <v>21.5064</v>
+        <v>22.1038</v>
       </c>
       <c r="G38">
         <v>1.69</v>
@@ -4531,28 +4531,28 @@
         <v>3.52</v>
       </c>
       <c r="M38">
-        <v>1.63018512</v>
+        <v>1.67546804</v>
       </c>
       <c r="N38">
-        <v>1.88981488</v>
+        <v>1.84453196</v>
       </c>
       <c r="O38">
-        <v>0.377962976</v>
+        <v>0.368906392</v>
       </c>
       <c r="P38">
-        <v>1.511851904</v>
+        <v>1.475625568</v>
       </c>
       <c r="Q38">
-        <v>1.171851904</v>
+        <v>1.135625568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2009860107200384</v>
+        <v>0.2031095193505808</v>
       </c>
       <c r="T38">
-        <v>2.400678230773375</v>
+        <v>2.433528233931193</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.159263973652268</v>
+        <v>2.100905487877883</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1503957971908659</v>
+        <v>0.1503301475209073</v>
       </c>
       <c r="C39">
-        <v>38.5977117751662</v>
+        <v>38.03737367896794</v>
       </c>
       <c r="D39">
-        <v>59.0115117751662</v>
+        <v>59.04857367896794</v>
       </c>
       <c r="E39">
-        <v>18.0638</v>
+        <v>18.6612</v>
       </c>
       <c r="F39">
-        <v>22.1038</v>
+        <v>22.7012</v>
       </c>
       <c r="G39">
         <v>1.69</v>
@@ -4613,28 +4613,28 @@
         <v>3.52</v>
       </c>
       <c r="M39">
-        <v>1.67546804</v>
+        <v>1.72075096</v>
       </c>
       <c r="N39">
-        <v>1.84453196</v>
+        <v>1.79924904</v>
       </c>
       <c r="O39">
-        <v>0.368906392</v>
+        <v>0.359849808</v>
       </c>
       <c r="P39">
-        <v>1.475625568</v>
+        <v>1.439399232</v>
       </c>
       <c r="Q39">
-        <v>1.135625568</v>
+        <v>1.099399232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2031095193505808</v>
+        <v>0.2053015282595278</v>
       </c>
       <c r="T39">
-        <v>2.433528233931193</v>
+        <v>2.467437914610231</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.100905487877883</v>
+        <v>2.045618501354781</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1503301475209073</v>
+        <v>0.1546948978509486</v>
       </c>
       <c r="C40">
-        <v>38.03737367896794</v>
+        <v>35.07317517380271</v>
       </c>
       <c r="D40">
-        <v>59.04857367896794</v>
+        <v>56.68177517380271</v>
       </c>
       <c r="E40">
-        <v>18.6612</v>
+        <v>19.2586</v>
       </c>
       <c r="F40">
-        <v>22.7012</v>
+        <v>23.2986</v>
       </c>
       <c r="G40">
         <v>1.69</v>
@@ -4695,45 +4695,45 @@
         <v>3.52</v>
       </c>
       <c r="M40">
-        <v>1.72075096</v>
+        <v>2.096874</v>
       </c>
       <c r="N40">
-        <v>1.79924904</v>
+        <v>1.423126</v>
       </c>
       <c r="O40">
-        <v>0.359849808</v>
+        <v>0.2846252</v>
       </c>
       <c r="P40">
-        <v>1.439399232</v>
+        <v>1.1385008</v>
       </c>
       <c r="Q40">
-        <v>1.099399232</v>
+        <v>0.7985008</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2053015282595278</v>
+        <v>0.2075654063130305</v>
       </c>
       <c r="T40">
-        <v>2.467437914610231</v>
+        <v>2.502459388098419</v>
       </c>
       <c r="U40">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.045618501354781</v>
+        <v>1.678689325157353</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1546948978509486</v>
+        <v>0.1547428481809899</v>
       </c>
       <c r="C41">
-        <v>35.07317517380271</v>
+        <v>34.45082714029439</v>
       </c>
       <c r="D41">
-        <v>56.68177517380271</v>
+        <v>56.65682714029439</v>
       </c>
       <c r="E41">
-        <v>19.2586</v>
+        <v>19.856</v>
       </c>
       <c r="F41">
-        <v>23.2986</v>
+        <v>23.896</v>
       </c>
       <c r="G41">
         <v>1.69</v>
@@ -4777,28 +4777,28 @@
         <v>3.52</v>
       </c>
       <c r="M41">
-        <v>2.096874</v>
+        <v>2.15064</v>
       </c>
       <c r="N41">
-        <v>1.423126</v>
+        <v>1.36936</v>
       </c>
       <c r="O41">
-        <v>0.2846252</v>
+        <v>0.273872</v>
       </c>
       <c r="P41">
-        <v>1.1385008</v>
+        <v>1.095488</v>
       </c>
       <c r="Q41">
-        <v>0.7985008</v>
+        <v>0.7554880000000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2075654063130305</v>
+        <v>0.2099047469683165</v>
       </c>
       <c r="T41">
-        <v>2.502459388098419</v>
+        <v>2.538648244036212</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.678689325157353</v>
+        <v>1.636722092028419</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1547428481809899</v>
+        <v>0.1547907985110312</v>
       </c>
       <c r="C42">
-        <v>34.45082714029439</v>
+        <v>33.82850105848211</v>
       </c>
       <c r="D42">
-        <v>56.65682714029439</v>
+        <v>56.63190105848211</v>
       </c>
       <c r="E42">
-        <v>19.856</v>
+        <v>20.4534</v>
       </c>
       <c r="F42">
-        <v>23.896</v>
+        <v>24.4934</v>
       </c>
       <c r="G42">
         <v>1.69</v>
@@ -4859,28 +4859,28 @@
         <v>3.52</v>
       </c>
       <c r="M42">
-        <v>2.15064</v>
+        <v>2.204406</v>
       </c>
       <c r="N42">
-        <v>1.36936</v>
+        <v>1.315594</v>
       </c>
       <c r="O42">
-        <v>0.273872</v>
+        <v>0.2631188</v>
       </c>
       <c r="P42">
-        <v>1.095488</v>
+        <v>1.0524752</v>
       </c>
       <c r="Q42">
-        <v>0.7554880000000002</v>
+        <v>0.7124752000000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2099047469683165</v>
+        <v>0.2123233873068326</v>
       </c>
       <c r="T42">
-        <v>2.538648244036212</v>
+        <v>2.576063840853253</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.636722092028419</v>
+        <v>1.596802041003336</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1547907985110312</v>
+        <v>0.1548387488410726</v>
       </c>
       <c r="C43">
-        <v>33.82850105848211</v>
+        <v>33.20619689940577</v>
       </c>
       <c r="D43">
-        <v>56.63190105848211</v>
+        <v>56.60699689940577</v>
       </c>
       <c r="E43">
-        <v>20.4534</v>
+        <v>21.0508</v>
       </c>
       <c r="F43">
-        <v>24.4934</v>
+        <v>25.0908</v>
       </c>
       <c r="G43">
         <v>1.69</v>
@@ -4941,28 +4941,28 @@
         <v>3.52</v>
       </c>
       <c r="M43">
-        <v>2.204406</v>
+        <v>2.258172</v>
       </c>
       <c r="N43">
-        <v>1.315594</v>
+        <v>1.261828</v>
       </c>
       <c r="O43">
-        <v>0.2631188</v>
+        <v>0.2523656</v>
       </c>
       <c r="P43">
-        <v>1.0524752</v>
+        <v>1.0094624</v>
       </c>
       <c r="Q43">
-        <v>0.7124752000000001</v>
+        <v>0.6694624</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2123233873068326</v>
+        <v>0.214825429036332</v>
       </c>
       <c r="T43">
-        <v>2.576063840853253</v>
+        <v>2.614769630663985</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.596802041003336</v>
+        <v>1.558782944788971</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1548387488410726</v>
+        <v>0.1548866991711139</v>
       </c>
       <c r="C44">
-        <v>33.20619689940577</v>
+        <v>32.58391463415622</v>
       </c>
       <c r="D44">
-        <v>56.60699689940577</v>
+        <v>56.58211463415622</v>
       </c>
       <c r="E44">
-        <v>21.0508</v>
+        <v>21.6482</v>
       </c>
       <c r="F44">
-        <v>25.0908</v>
+        <v>25.6882</v>
       </c>
       <c r="G44">
         <v>1.69</v>
@@ -5023,28 +5023,28 @@
         <v>3.52</v>
       </c>
       <c r="M44">
-        <v>2.258172</v>
+        <v>2.311938</v>
       </c>
       <c r="N44">
-        <v>1.261828</v>
+        <v>1.208062</v>
       </c>
       <c r="O44">
-        <v>0.2523656</v>
+        <v>0.2416124</v>
       </c>
       <c r="P44">
-        <v>1.0094624</v>
+        <v>0.9664496</v>
       </c>
       <c r="Q44">
-        <v>0.6694624</v>
+        <v>0.6264496000000002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.214825429036332</v>
+        <v>0.2174152617037086</v>
       </c>
       <c r="T44">
-        <v>2.614769630663984</v>
+        <v>2.654833518362813</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.558782944788971</v>
+        <v>1.522532178631088</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1548866991711139</v>
+        <v>0.1768889961006157</v>
       </c>
       <c r="C45">
-        <v>32.58391463415622</v>
+        <v>22.48963446791954</v>
       </c>
       <c r="D45">
-        <v>56.58211463415622</v>
+        <v>47.08523446791955</v>
       </c>
       <c r="E45">
-        <v>21.6482</v>
+        <v>22.2456</v>
       </c>
       <c r="F45">
-        <v>25.6882</v>
+        <v>26.2856</v>
       </c>
       <c r="G45">
         <v>1.69</v>
@@ -5105,45 +5105,45 @@
         <v>3.52</v>
       </c>
       <c r="M45">
-        <v>2.311938</v>
+        <v>3.858726080000001</v>
       </c>
       <c r="N45">
-        <v>1.208062</v>
+        <v>-0.3387260800000007</v>
       </c>
       <c r="O45">
-        <v>0.2416124</v>
+        <v>-0.06774521600000015</v>
       </c>
       <c r="P45">
-        <v>0.9664496</v>
+        <v>-0.2709808640000005</v>
       </c>
       <c r="Q45">
-        <v>0.6264496000000002</v>
+        <v>-0.6109808640000004</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2174152617037086</v>
+        <v>0.2215739199343219</v>
       </c>
       <c r="T45">
-        <v>2.654833518362813</v>
+        <v>2.719166638578596</v>
       </c>
       <c r="U45">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2</v>
+        <v>0.1824436317594225</v>
       </c>
       <c r="W45">
-        <v>0.07199999999999999</v>
+        <v>0.1200172748577168</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.522532178631088</v>
+        <v>0.9122181587971124</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1768889961006157</v>
+        <v>0.1778989961006157</v>
       </c>
       <c r="C46">
-        <v>22.48963446791954</v>
+        <v>21.53223107488559</v>
       </c>
       <c r="D46">
-        <v>47.08523446791955</v>
+        <v>46.7252310748856</v>
       </c>
       <c r="E46">
-        <v>22.2456</v>
+        <v>22.843</v>
       </c>
       <c r="F46">
-        <v>26.2856</v>
+        <v>26.883</v>
       </c>
       <c r="G46">
         <v>1.69</v>
@@ -5187,37 +5187,37 @@
         <v>3.52</v>
       </c>
       <c r="M46">
-        <v>3.858726080000001</v>
+        <v>3.946424400000001</v>
       </c>
       <c r="N46">
-        <v>-0.3387260800000007</v>
+        <v>-0.4264244000000006</v>
       </c>
       <c r="O46">
-        <v>-0.06774521600000015</v>
+        <v>-0.08528488000000012</v>
       </c>
       <c r="P46">
-        <v>-0.2709808640000005</v>
+        <v>-0.3411395200000005</v>
       </c>
       <c r="Q46">
-        <v>-0.6109808640000004</v>
+        <v>-0.6811395200000003</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2215739199343219</v>
+        <v>0.2247698093876732</v>
       </c>
       <c r="T46">
-        <v>2.719166638578596</v>
+        <v>2.768606032007297</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1824436317594225</v>
+        <v>0.1783893288314354</v>
       </c>
       <c r="W46">
-        <v>0.1200172748577168</v>
+        <v>0.1206124465275453</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9122181587971124</v>
+        <v>0.8919466441571766</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1778989961006157</v>
+        <v>0.1789089961006157</v>
       </c>
       <c r="C47">
-        <v>21.53223107488559</v>
+        <v>20.58029092532304</v>
       </c>
       <c r="D47">
-        <v>46.7252310748856</v>
+        <v>46.37069092532305</v>
       </c>
       <c r="E47">
-        <v>22.843</v>
+        <v>23.4404</v>
       </c>
       <c r="F47">
-        <v>26.883</v>
+        <v>27.4804</v>
       </c>
       <c r="G47">
         <v>1.69</v>
@@ -5269,37 +5269,37 @@
         <v>3.52</v>
       </c>
       <c r="M47">
-        <v>3.946424400000001</v>
+        <v>4.034122720000001</v>
       </c>
       <c r="N47">
-        <v>-0.4264244000000006</v>
+        <v>-0.5141227200000009</v>
       </c>
       <c r="O47">
-        <v>-0.08528488000000012</v>
+        <v>-0.1028245440000002</v>
       </c>
       <c r="P47">
-        <v>-0.3411395200000005</v>
+        <v>-0.4112981760000007</v>
       </c>
       <c r="Q47">
-        <v>-0.6811395200000003</v>
+        <v>-0.7512981760000006</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2247698093876732</v>
+        <v>0.2280840651170746</v>
       </c>
       <c r="T47">
-        <v>2.768606032007297</v>
+        <v>2.819876514081507</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1783893288314354</v>
+        <v>0.1745112999437954</v>
       </c>
       <c r="W47">
-        <v>0.1206124465275453</v>
+        <v>0.1211817411682508</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8919466441571766</v>
+        <v>0.8725564997189771</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1789089961006157</v>
+        <v>0.1799189961006157</v>
       </c>
       <c r="C48">
-        <v>20.58029092532304</v>
+        <v>19.63369059430176</v>
       </c>
       <c r="D48">
-        <v>46.37069092532305</v>
+        <v>46.02149059430177</v>
       </c>
       <c r="E48">
-        <v>23.4404</v>
+        <v>24.0378</v>
       </c>
       <c r="F48">
-        <v>27.4804</v>
+        <v>28.0778</v>
       </c>
       <c r="G48">
         <v>1.69</v>
@@ -5351,37 +5351,37 @@
         <v>3.52</v>
       </c>
       <c r="M48">
-        <v>4.034122720000001</v>
+        <v>4.121821040000001</v>
       </c>
       <c r="N48">
-        <v>-0.5141227200000009</v>
+        <v>-0.6018210400000013</v>
       </c>
       <c r="O48">
-        <v>-0.1028245440000002</v>
+        <v>-0.1203642080000003</v>
       </c>
       <c r="P48">
-        <v>-0.4112981760000007</v>
+        <v>-0.481456832000001</v>
       </c>
       <c r="Q48">
-        <v>-0.7512981760000006</v>
+        <v>-0.8214568320000009</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2280840651170746</v>
+        <v>0.2315233871004156</v>
       </c>
       <c r="T48">
-        <v>2.819876514081507</v>
+        <v>2.873081731328328</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1745112999437954</v>
+        <v>0.1707982935620125</v>
       </c>
       <c r="W48">
-        <v>0.1211817411682508</v>
+        <v>0.1217268105050966</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8725564997189771</v>
+        <v>0.8539914678100626</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1799189961006157</v>
+        <v>0.1809289961006157</v>
       </c>
       <c r="C49">
-        <v>19.63369059430176</v>
+        <v>18.69231034697102</v>
       </c>
       <c r="D49">
-        <v>46.02149059430177</v>
+        <v>45.67751034697103</v>
       </c>
       <c r="E49">
-        <v>24.0378</v>
+        <v>24.6352</v>
       </c>
       <c r="F49">
-        <v>28.0778</v>
+        <v>28.6752</v>
       </c>
       <c r="G49">
         <v>1.69</v>
@@ -5433,37 +5433,37 @@
         <v>3.52</v>
       </c>
       <c r="M49">
-        <v>4.121821040000001</v>
+        <v>4.209519360000001</v>
       </c>
       <c r="N49">
-        <v>-0.6018210400000013</v>
+        <v>-0.6895193600000007</v>
       </c>
       <c r="O49">
-        <v>-0.1203642080000003</v>
+        <v>-0.1379038720000001</v>
       </c>
       <c r="P49">
-        <v>-0.481456832000001</v>
+        <v>-0.5516154880000006</v>
       </c>
       <c r="Q49">
-        <v>-0.8214568320000009</v>
+        <v>-0.8916154880000005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2315233871004156</v>
+        <v>0.2350949906985006</v>
       </c>
       <c r="T49">
-        <v>2.873081731328328</v>
+        <v>2.928333303084642</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1707982935620125</v>
+        <v>0.1672399957794706</v>
       </c>
       <c r="W49">
-        <v>0.1217268105050966</v>
+        <v>0.1222491686195737</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8539914678100626</v>
+        <v>0.8361999788973531</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1809289961006157</v>
+        <v>0.1819389961006157</v>
       </c>
       <c r="C50">
-        <v>18.69231034697102</v>
+        <v>17.75603400167796</v>
       </c>
       <c r="D50">
-        <v>45.67751034697103</v>
+        <v>45.33863400167797</v>
       </c>
       <c r="E50">
-        <v>24.6352</v>
+        <v>25.2326</v>
       </c>
       <c r="F50">
-        <v>28.6752</v>
+        <v>29.2726</v>
       </c>
       <c r="G50">
         <v>1.69</v>
@@ -5515,37 +5515,37 @@
         <v>3.52</v>
       </c>
       <c r="M50">
-        <v>4.209519360000001</v>
+        <v>4.29721768</v>
       </c>
       <c r="N50">
-        <v>-0.6895193600000007</v>
+        <v>-0.7772176800000001</v>
       </c>
       <c r="O50">
-        <v>-0.1379038720000001</v>
+        <v>-0.155443536</v>
       </c>
       <c r="P50">
-        <v>-0.5516154880000006</v>
+        <v>-0.6217741440000001</v>
       </c>
       <c r="Q50">
-        <v>-0.8916154880000005</v>
+        <v>-0.9617741439999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2350949906985006</v>
+        <v>0.2388066571827849</v>
       </c>
       <c r="T50">
-        <v>2.928333303084642</v>
+        <v>2.985751603145125</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1672399957794706</v>
+        <v>0.1638269346411141</v>
       </c>
       <c r="W50">
-        <v>0.1222491686195737</v>
+        <v>0.1227502059946845</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8361999788973531</v>
+        <v>0.8191346732055705</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1819389961006157</v>
+        <v>0.1829489961006157</v>
       </c>
       <c r="C51">
-        <v>17.75603400167796</v>
+        <v>16.82474879913445</v>
       </c>
       <c r="D51">
-        <v>45.33863400167797</v>
+        <v>45.00474879913445</v>
       </c>
       <c r="E51">
-        <v>25.2326</v>
+        <v>25.83</v>
       </c>
       <c r="F51">
-        <v>29.2726</v>
+        <v>29.87</v>
       </c>
       <c r="G51">
         <v>1.69</v>
@@ -5597,37 +5597,37 @@
         <v>3.52</v>
       </c>
       <c r="M51">
-        <v>4.29721768</v>
+        <v>4.384916</v>
       </c>
       <c r="N51">
-        <v>-0.7772176800000001</v>
+        <v>-0.8649160000000005</v>
       </c>
       <c r="O51">
-        <v>-0.155443536</v>
+        <v>-0.1729832000000001</v>
       </c>
       <c r="P51">
-        <v>-0.6217741440000001</v>
+        <v>-0.6919328000000003</v>
       </c>
       <c r="Q51">
-        <v>-0.9617741439999999</v>
+        <v>-1.0319328</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2388066571827849</v>
+        <v>0.2426667903264406</v>
       </c>
       <c r="T51">
-        <v>2.985751603145125</v>
+        <v>3.045466635208027</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1638269346411141</v>
+        <v>0.1605503959482918</v>
       </c>
       <c r="W51">
-        <v>0.1227502059946845</v>
+        <v>0.1232312018747908</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8191346732055705</v>
+        <v>0.8027519797414591</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1829489961006157</v>
+        <v>0.2138094430631171</v>
       </c>
       <c r="C52">
-        <v>16.82474879913445</v>
+        <v>7.960749981503557</v>
       </c>
       <c r="D52">
-        <v>45.00474879913445</v>
+        <v>36.73814998150356</v>
       </c>
       <c r="E52">
-        <v>25.83</v>
+        <v>26.4274</v>
       </c>
       <c r="F52">
-        <v>29.87</v>
+        <v>30.4674</v>
       </c>
       <c r="G52">
         <v>1.69</v>
@@ -5679,45 +5679,45 @@
         <v>3.52</v>
       </c>
       <c r="M52">
-        <v>4.384916</v>
+        <v>6.117853920000001</v>
       </c>
       <c r="N52">
-        <v>-0.8649160000000005</v>
+        <v>-2.597853920000001</v>
       </c>
       <c r="O52">
-        <v>-0.1729832000000001</v>
+        <v>-0.5195707840000002</v>
       </c>
       <c r="P52">
-        <v>-0.6919328000000003</v>
+        <v>-2.078283136</v>
       </c>
       <c r="Q52">
-        <v>-1.0319328</v>
+        <v>-2.418283136</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2426667903264406</v>
+        <v>0.2513996778075954</v>
       </c>
       <c r="T52">
-        <v>3.045466635208027</v>
+        <v>3.180561627150459</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1605503959482918</v>
+        <v>0.115073032015122</v>
       </c>
       <c r="W52">
-        <v>0.1232312018747908</v>
+        <v>0.1776933351713635</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8027519797414591</v>
+        <v>0.5753651600756102</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2138094430631171</v>
+        <v>0.2153594430631171</v>
       </c>
       <c r="C53">
-        <v>7.960749981503557</v>
+        <v>7.027514174056758</v>
       </c>
       <c r="D53">
-        <v>36.73814998150356</v>
+        <v>36.40231417405676</v>
       </c>
       <c r="E53">
-        <v>26.4274</v>
+        <v>27.0248</v>
       </c>
       <c r="F53">
-        <v>30.4674</v>
+        <v>31.0648</v>
       </c>
       <c r="G53">
         <v>1.69</v>
@@ -5761,37 +5761,37 @@
         <v>3.52</v>
       </c>
       <c r="M53">
-        <v>6.117853920000001</v>
+        <v>6.237811840000001</v>
       </c>
       <c r="N53">
-        <v>-2.597853920000001</v>
+        <v>-2.717811840000001</v>
       </c>
       <c r="O53">
-        <v>-0.5195707840000002</v>
+        <v>-0.5435623680000002</v>
       </c>
       <c r="P53">
-        <v>-2.078283136</v>
+        <v>-2.174249472000001</v>
       </c>
       <c r="Q53">
-        <v>-2.418283136</v>
+        <v>-2.514249472</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2513996778075954</v>
+        <v>0.255683004428587</v>
       </c>
       <c r="T53">
-        <v>3.180561627150459</v>
+        <v>3.246823327716094</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.115073032015122</v>
+        <v>0.1128600890917543</v>
       </c>
       <c r="W53">
-        <v>0.1776933351713635</v>
+        <v>0.1781376941103757</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5753651600756102</v>
+        <v>0.5643004454587716</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2153594430631171</v>
+        <v>0.2169094430631171</v>
       </c>
       <c r="C54">
-        <v>7.027514174056758</v>
+        <v>6.100362723992287</v>
       </c>
       <c r="D54">
-        <v>36.40231417405676</v>
+        <v>36.07256272399229</v>
       </c>
       <c r="E54">
-        <v>27.0248</v>
+        <v>27.6222</v>
       </c>
       <c r="F54">
-        <v>31.0648</v>
+        <v>31.6622</v>
       </c>
       <c r="G54">
         <v>1.69</v>
@@ -5843,37 +5843,37 @@
         <v>3.52</v>
       </c>
       <c r="M54">
-        <v>6.237811840000001</v>
+        <v>6.357769760000001</v>
       </c>
       <c r="N54">
-        <v>-2.717811840000001</v>
+        <v>-2.837769760000001</v>
       </c>
       <c r="O54">
-        <v>-0.5435623680000002</v>
+        <v>-0.5675539520000003</v>
       </c>
       <c r="P54">
-        <v>-2.174249472000001</v>
+        <v>-2.270215808000001</v>
       </c>
       <c r="Q54">
-        <v>-2.514249472</v>
+        <v>-2.610215808</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.255683004428587</v>
+        <v>0.2601486002674931</v>
       </c>
       <c r="T54">
-        <v>3.246823327716094</v>
+        <v>3.315904675114309</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1128600890917543</v>
+        <v>0.1107306534485137</v>
       </c>
       <c r="W54">
-        <v>0.1781376941103757</v>
+        <v>0.1785652847875384</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5643004454587716</v>
+        <v>0.5536532672425682</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2169094430631171</v>
+        <v>0.2184594430631171</v>
       </c>
       <c r="C55">
-        <v>6.100362723992287</v>
+        <v>5.179131769656642</v>
       </c>
       <c r="D55">
-        <v>36.07256272399229</v>
+        <v>35.74873176965665</v>
       </c>
       <c r="E55">
-        <v>27.6222</v>
+        <v>28.21960000000001</v>
       </c>
       <c r="F55">
-        <v>31.6622</v>
+        <v>32.25960000000001</v>
       </c>
       <c r="G55">
         <v>1.69</v>
@@ -5925,37 +5925,37 @@
         <v>3.52</v>
       </c>
       <c r="M55">
-        <v>6.357769760000001</v>
+        <v>6.477727680000001</v>
       </c>
       <c r="N55">
-        <v>-2.837769760000001</v>
+        <v>-2.957727680000001</v>
       </c>
       <c r="O55">
-        <v>-0.5675539520000003</v>
+        <v>-0.5915455360000003</v>
       </c>
       <c r="P55">
-        <v>-2.270215808000001</v>
+        <v>-2.366182144000001</v>
       </c>
       <c r="Q55">
-        <v>-2.610215808</v>
+        <v>-2.706182144</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2601486002674931</v>
+        <v>0.2648083524472212</v>
       </c>
       <c r="T55">
-        <v>3.315904675114309</v>
+        <v>3.387989559355924</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1107306534485137</v>
+        <v>0.1086800857920597</v>
       </c>
       <c r="W55">
-        <v>0.1785652847875384</v>
+        <v>0.1789770387729544</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5536532672425682</v>
+        <v>0.5434004289602985</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2184594430631171</v>
+        <v>0.2200094430631171</v>
       </c>
       <c r="C56">
-        <v>5.179131769656642</v>
+        <v>4.263663281125325</v>
       </c>
       <c r="D56">
-        <v>35.74873176965665</v>
+        <v>35.43066328112533</v>
       </c>
       <c r="E56">
-        <v>28.21960000000001</v>
+        <v>28.81700000000001</v>
       </c>
       <c r="F56">
-        <v>32.25960000000001</v>
+        <v>32.85700000000001</v>
       </c>
       <c r="G56">
         <v>1.69</v>
@@ -6007,37 +6007,37 @@
         <v>3.52</v>
       </c>
       <c r="M56">
-        <v>6.477727680000001</v>
+        <v>6.597685600000002</v>
       </c>
       <c r="N56">
-        <v>-2.957727680000001</v>
+        <v>-3.077685600000002</v>
       </c>
       <c r="O56">
-        <v>-0.5915455360000003</v>
+        <v>-0.6155371200000004</v>
       </c>
       <c r="P56">
-        <v>-2.366182144000001</v>
+        <v>-2.462148480000002</v>
       </c>
       <c r="Q56">
-        <v>-2.706182144</v>
+        <v>-2.802148480000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2648083524472212</v>
+        <v>0.2696752047238261</v>
       </c>
       <c r="T56">
-        <v>3.387989559355924</v>
+        <v>3.4632782162305</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1086800857920597</v>
+        <v>0.1067040842322041</v>
       </c>
       <c r="W56">
-        <v>0.1789770387729544</v>
+        <v>0.1793738198861734</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5434004289602985</v>
+        <v>0.5335204211610203</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2200094430631171</v>
+        <v>0.2215594430631171</v>
       </c>
       <c r="C57">
-        <v>4.263663281125325</v>
+        <v>3.353804803056398</v>
       </c>
       <c r="D57">
-        <v>35.43066328112533</v>
+        <v>35.11820480305641</v>
       </c>
       <c r="E57">
-        <v>28.81700000000001</v>
+        <v>29.41440000000001</v>
       </c>
       <c r="F57">
-        <v>32.85700000000001</v>
+        <v>33.45440000000001</v>
       </c>
       <c r="G57">
         <v>1.69</v>
@@ -6089,37 +6089,37 @@
         <v>3.52</v>
       </c>
       <c r="M57">
-        <v>6.597685600000002</v>
+        <v>6.717643520000002</v>
       </c>
       <c r="N57">
-        <v>-3.077685600000002</v>
+        <v>-3.197643520000002</v>
       </c>
       <c r="O57">
-        <v>-0.6155371200000004</v>
+        <v>-0.6395287040000004</v>
       </c>
       <c r="P57">
-        <v>-2.462148480000002</v>
+        <v>-2.558114816000002</v>
       </c>
       <c r="Q57">
-        <v>-2.802148480000001</v>
+        <v>-2.898114816000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2696752047238261</v>
+        <v>0.2747632775584585</v>
       </c>
       <c r="T57">
-        <v>3.4632782162305</v>
+        <v>3.541989084781194</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1067040842322041</v>
+        <v>0.104798654156629</v>
       </c>
       <c r="W57">
-        <v>0.1793738198861734</v>
+        <v>0.1797564302453489</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5335204211610203</v>
+        <v>0.5239932707831449</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2215594430631171</v>
+        <v>0.2231094430631171</v>
       </c>
       <c r="C58">
-        <v>3.353804803056398</v>
+        <v>2.449409211031664</v>
       </c>
       <c r="D58">
-        <v>35.11820480305641</v>
+        <v>34.81120921103167</v>
       </c>
       <c r="E58">
-        <v>29.41440000000001</v>
+        <v>30.01180000000001</v>
       </c>
       <c r="F58">
-        <v>33.45440000000001</v>
+        <v>34.05180000000001</v>
       </c>
       <c r="G58">
         <v>1.69</v>
@@ -6171,37 +6171,37 @@
         <v>3.52</v>
       </c>
       <c r="M58">
-        <v>6.717643520000002</v>
+        <v>6.837601440000002</v>
       </c>
       <c r="N58">
-        <v>-3.197643520000002</v>
+        <v>-3.317601440000002</v>
       </c>
       <c r="O58">
-        <v>-0.6395287040000004</v>
+        <v>-0.6635202880000004</v>
       </c>
       <c r="P58">
-        <v>-2.558114816000002</v>
+        <v>-2.654081152000002</v>
       </c>
       <c r="Q58">
-        <v>-2.898114816000001</v>
+        <v>-2.994081152000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2747632775584585</v>
+        <v>0.280088004943539</v>
       </c>
       <c r="T58">
-        <v>3.541989084781194</v>
+        <v>3.624360923962151</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.104798654156629</v>
+        <v>0.1029600812766881</v>
       </c>
       <c r="W58">
-        <v>0.1797564302453489</v>
+        <v>0.180125615679641</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5239932707831449</v>
+        <v>0.5148004063834406</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2231094430631171</v>
+        <v>0.2246594430631171</v>
       </c>
       <c r="C59">
-        <v>2.449409211031664</v>
+        <v>1.550334480567152</v>
       </c>
       <c r="D59">
-        <v>34.81120921103167</v>
+        <v>34.50953448056716</v>
       </c>
       <c r="E59">
-        <v>30.01180000000001</v>
+        <v>30.60920000000001</v>
       </c>
       <c r="F59">
-        <v>34.05180000000001</v>
+        <v>34.64920000000001</v>
       </c>
       <c r="G59">
         <v>1.69</v>
@@ -6253,37 +6253,37 @@
         <v>3.52</v>
       </c>
       <c r="M59">
-        <v>6.837601440000002</v>
+        <v>6.957559360000002</v>
       </c>
       <c r="N59">
-        <v>-3.317601440000002</v>
+        <v>-3.437559360000002</v>
       </c>
       <c r="O59">
-        <v>-0.6635202880000004</v>
+        <v>-0.6875118720000004</v>
       </c>
       <c r="P59">
-        <v>-2.654081152000002</v>
+        <v>-2.750047488000002</v>
       </c>
       <c r="Q59">
-        <v>-2.994081152000001</v>
+        <v>-3.090047488000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.280088004943539</v>
+        <v>0.285666290775528</v>
       </c>
       <c r="T59">
-        <v>3.624360923962151</v>
+        <v>3.710655231675536</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1029600812766881</v>
+        <v>0.1011849074615728</v>
       </c>
       <c r="W59">
-        <v>0.180125615679641</v>
+        <v>0.1804820705817162</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5148004063834406</v>
+        <v>0.505924537307864</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2246594430631171</v>
+        <v>0.2477917363195909</v>
       </c>
       <c r="C60">
-        <v>1.550334480567166</v>
+        <v>-2.999131511310004</v>
       </c>
       <c r="D60">
-        <v>34.50953448056717</v>
+        <v>30.55746848869</v>
       </c>
       <c r="E60">
-        <v>30.6092</v>
+        <v>31.2066</v>
       </c>
       <c r="F60">
-        <v>34.6492</v>
+        <v>35.2466</v>
       </c>
       <c r="G60">
         <v>1.69</v>
@@ -6335,45 +6335,45 @@
         <v>3.52</v>
       </c>
       <c r="M60">
-        <v>6.95755936</v>
+        <v>8.311148280000001</v>
       </c>
       <c r="N60">
-        <v>-3.43755936</v>
+        <v>-4.791148280000002</v>
       </c>
       <c r="O60">
-        <v>-0.6875118720000001</v>
+        <v>-0.9582296560000003</v>
       </c>
       <c r="P60">
-        <v>-2.750047488</v>
+        <v>-3.832918624000001</v>
       </c>
       <c r="Q60">
-        <v>-3.090047488</v>
+        <v>-4.172918624000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2856662907755279</v>
+        <v>0.293790574102916</v>
       </c>
       <c r="T60">
-        <v>3.710655231675535</v>
+        <v>3.83633531091851</v>
       </c>
       <c r="U60">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1011849074615729</v>
+        <v>0.08470550353362243</v>
       </c>
       <c r="W60">
-        <v>0.1804820705817162</v>
+        <v>0.2158264422667719</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5059245373078642</v>
+        <v>0.423527517668112</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2477917363195909</v>
+        <v>0.2496917363195909</v>
       </c>
       <c r="C61">
-        <v>-2.999131511310004</v>
+        <v>-3.881286505193156</v>
       </c>
       <c r="D61">
-        <v>30.55746848869</v>
+        <v>30.27271349480684</v>
       </c>
       <c r="E61">
-        <v>31.2066</v>
+        <v>31.804</v>
       </c>
       <c r="F61">
-        <v>35.2466</v>
+        <v>35.844</v>
       </c>
       <c r="G61">
         <v>1.69</v>
@@ -6417,37 +6417,37 @@
         <v>3.52</v>
       </c>
       <c r="M61">
-        <v>8.311148280000001</v>
+        <v>8.4520152</v>
       </c>
       <c r="N61">
-        <v>-4.791148280000002</v>
+        <v>-4.9320152</v>
       </c>
       <c r="O61">
-        <v>-0.9582296560000003</v>
+        <v>-0.9864030400000001</v>
       </c>
       <c r="P61">
-        <v>-3.832918624000001</v>
+        <v>-3.94561216</v>
       </c>
       <c r="Q61">
-        <v>-4.172918624000001</v>
+        <v>-4.28561216</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.293790574102916</v>
+        <v>0.2999903384554889</v>
       </c>
       <c r="T61">
-        <v>3.83633531091851</v>
+        <v>3.932243693691473</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08470550353362243</v>
+        <v>0.0832937451413954</v>
       </c>
       <c r="W61">
-        <v>0.2158264422667719</v>
+        <v>0.216159334895659</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.423527517668112</v>
+        <v>0.4164687257069769</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2496917363195909</v>
+        <v>0.251591736319591</v>
       </c>
       <c r="C62">
-        <v>-3.881286505193156</v>
+        <v>-4.758183421195696</v>
       </c>
       <c r="D62">
-        <v>30.27271349480684</v>
+        <v>29.9932165788043</v>
       </c>
       <c r="E62">
-        <v>31.804</v>
+        <v>32.4014</v>
       </c>
       <c r="F62">
-        <v>35.844</v>
+        <v>36.4414</v>
       </c>
       <c r="G62">
         <v>1.69</v>
@@ -6499,37 +6499,37 @@
         <v>3.52</v>
       </c>
       <c r="M62">
-        <v>8.4520152</v>
+        <v>8.592882120000001</v>
       </c>
       <c r="N62">
-        <v>-4.9320152</v>
+        <v>-5.072882120000001</v>
       </c>
       <c r="O62">
-        <v>-0.9864030400000001</v>
+        <v>-1.014576424</v>
       </c>
       <c r="P62">
-        <v>-3.94561216</v>
+        <v>-4.058305696000001</v>
       </c>
       <c r="Q62">
-        <v>-4.28561216</v>
+        <v>-4.398305696</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2999903384554889</v>
+        <v>0.3065080394415272</v>
       </c>
       <c r="T62">
-        <v>3.932243693691473</v>
+        <v>4.033070455068178</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0832937451413954</v>
+        <v>0.08192827390956925</v>
       </c>
       <c r="W62">
-        <v>0.216159334895659</v>
+        <v>0.2164813130121236</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4164687257069769</v>
+        <v>0.4096413695478461</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.251591736319591</v>
+        <v>0.253491736319591</v>
       </c>
       <c r="C63">
-        <v>-4.758183421195696</v>
+        <v>-5.629966564740883</v>
       </c>
       <c r="D63">
-        <v>29.9932165788043</v>
+        <v>29.71883343525912</v>
       </c>
       <c r="E63">
-        <v>32.4014</v>
+        <v>32.9988</v>
       </c>
       <c r="F63">
-        <v>36.4414</v>
+        <v>37.0388</v>
       </c>
       <c r="G63">
         <v>1.69</v>
@@ -6581,37 +6581,37 @@
         <v>3.52</v>
       </c>
       <c r="M63">
-        <v>8.592882120000001</v>
+        <v>8.733749040000001</v>
       </c>
       <c r="N63">
-        <v>-5.072882120000001</v>
+        <v>-5.213749040000002</v>
       </c>
       <c r="O63">
-        <v>-1.014576424</v>
+        <v>-1.042749808</v>
       </c>
       <c r="P63">
-        <v>-4.058305696000001</v>
+        <v>-4.170999232000002</v>
       </c>
       <c r="Q63">
-        <v>-4.398305696</v>
+        <v>-4.510999232000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3065080394415272</v>
+        <v>0.3133687773215673</v>
       </c>
       <c r="T63">
-        <v>4.033070455068178</v>
+        <v>4.139203888096288</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08192827390956925</v>
+        <v>0.08060685013683425</v>
       </c>
       <c r="W63">
-        <v>0.2164813130121236</v>
+        <v>0.2167929047377345</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4096413695478461</v>
+        <v>0.4030342506841712</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.253491736319591</v>
+        <v>0.2553917363195909</v>
       </c>
       <c r="C64">
-        <v>-5.629966564740883</v>
+        <v>-6.49677500859714</v>
       </c>
       <c r="D64">
-        <v>29.71883343525912</v>
+        <v>29.44942499140286</v>
       </c>
       <c r="E64">
-        <v>32.9988</v>
+        <v>33.5962</v>
       </c>
       <c r="F64">
-        <v>37.0388</v>
+        <v>37.6362</v>
       </c>
       <c r="G64">
         <v>1.69</v>
@@ -6663,37 +6663,37 @@
         <v>3.52</v>
       </c>
       <c r="M64">
-        <v>8.733749040000001</v>
+        <v>8.874615960000002</v>
       </c>
       <c r="N64">
-        <v>-5.213749040000002</v>
+        <v>-5.354615960000002</v>
       </c>
       <c r="O64">
-        <v>-1.042749808</v>
+        <v>-1.070923192</v>
       </c>
       <c r="P64">
-        <v>-4.170999232000002</v>
+        <v>-4.283692768000002</v>
       </c>
       <c r="Q64">
-        <v>-4.510999232000001</v>
+        <v>-4.623692768000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3133687773215673</v>
+        <v>0.3206003658978259</v>
       </c>
       <c r="T64">
-        <v>4.139203888096288</v>
+        <v>4.251074263450241</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08060685013683425</v>
+        <v>0.07932737632513846</v>
       </c>
       <c r="W64">
-        <v>0.2167929047377345</v>
+        <v>0.2170946046625324</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4030342506841712</v>
+        <v>0.3966368816256922</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2553917363195909</v>
+        <v>0.257291736319591</v>
       </c>
       <c r="C65">
-        <v>-6.49677500859714</v>
+        <v>-7.358742827923724</v>
       </c>
       <c r="D65">
-        <v>29.44942499140286</v>
+        <v>29.18485717207628</v>
       </c>
       <c r="E65">
-        <v>33.5962</v>
+        <v>34.1936</v>
       </c>
       <c r="F65">
-        <v>37.6362</v>
+        <v>38.2336</v>
       </c>
       <c r="G65">
         <v>1.69</v>
@@ -6745,37 +6745,37 @@
         <v>3.52</v>
       </c>
       <c r="M65">
-        <v>8.874615960000002</v>
+        <v>9.01548288</v>
       </c>
       <c r="N65">
-        <v>-5.354615960000002</v>
+        <v>-5.495482880000001</v>
       </c>
       <c r="O65">
-        <v>-1.070923192</v>
+        <v>-1.099096576</v>
       </c>
       <c r="P65">
-        <v>-4.283692768000002</v>
+        <v>-4.396386304000001</v>
       </c>
       <c r="Q65">
-        <v>-4.623692768000002</v>
+        <v>-4.736386304000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3206003658978259</v>
+        <v>0.3282337093949877</v>
       </c>
       <c r="T65">
-        <v>4.251074263450241</v>
+        <v>4.369159659657193</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07932737632513846</v>
+        <v>0.07808788607005818</v>
       </c>
       <c r="W65">
-        <v>0.2170946046625324</v>
+        <v>0.2173868764646803</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3966368816256922</v>
+        <v>0.3904394303502908</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.257291736319591</v>
+        <v>0.259191736319591</v>
       </c>
       <c r="C66">
-        <v>-7.358742827923724</v>
+        <v>-8.215999322759572</v>
       </c>
       <c r="D66">
-        <v>29.18485717207628</v>
+        <v>28.92500067724043</v>
       </c>
       <c r="E66">
-        <v>34.1936</v>
+        <v>34.791</v>
       </c>
       <c r="F66">
-        <v>38.2336</v>
+        <v>38.831</v>
       </c>
       <c r="G66">
         <v>1.69</v>
@@ -6827,37 +6827,37 @@
         <v>3.52</v>
       </c>
       <c r="M66">
-        <v>9.01548288</v>
+        <v>9.156349800000001</v>
       </c>
       <c r="N66">
-        <v>-5.495482880000001</v>
+        <v>-5.636349800000001</v>
       </c>
       <c r="O66">
-        <v>-1.099096576</v>
+        <v>-1.12726996</v>
       </c>
       <c r="P66">
-        <v>-4.396386304000001</v>
+        <v>-4.509079840000001</v>
       </c>
       <c r="Q66">
-        <v>-4.736386304000001</v>
+        <v>-4.849079840000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3282337093949877</v>
+        <v>0.3363032439491302</v>
       </c>
       <c r="T66">
-        <v>4.369159659657193</v>
+        <v>4.493992792790256</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07808788607005818</v>
+        <v>0.07688653397667267</v>
       </c>
       <c r="W66">
-        <v>0.2173868764646803</v>
+        <v>0.2176701552883006</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3904394303502908</v>
+        <v>0.3844326698833632</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.259191736319591</v>
+        <v>0.2610917363195909</v>
       </c>
       <c r="C67">
-        <v>-8.215999322759572</v>
+        <v>-9.068669228731132</v>
       </c>
       <c r="D67">
-        <v>28.92500067724043</v>
+        <v>28.66973077126887</v>
       </c>
       <c r="E67">
-        <v>34.791</v>
+        <v>35.3884</v>
       </c>
       <c r="F67">
-        <v>38.831</v>
+        <v>39.4284</v>
       </c>
       <c r="G67">
         <v>1.69</v>
@@ -6909,37 +6909,37 @@
         <v>3.52</v>
       </c>
       <c r="M67">
-        <v>9.156349800000001</v>
+        <v>9.297216720000002</v>
       </c>
       <c r="N67">
-        <v>-5.636349800000001</v>
+        <v>-5.777216720000002</v>
       </c>
       <c r="O67">
-        <v>-1.12726996</v>
+        <v>-1.155443344</v>
       </c>
       <c r="P67">
-        <v>-4.509079840000001</v>
+        <v>-4.621773376000002</v>
       </c>
       <c r="Q67">
-        <v>-4.849079840000001</v>
+        <v>-4.961773376000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3363032439491302</v>
+        <v>0.3448474570064576</v>
       </c>
       <c r="T67">
-        <v>4.493992792790256</v>
+        <v>4.626169051401734</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07688653397667267</v>
+        <v>0.07572158649217763</v>
       </c>
       <c r="W67">
-        <v>0.2176701552883006</v>
+        <v>0.2179448499051445</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3844326698833632</v>
+        <v>0.3786079324608881</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2610917363195909</v>
+        <v>0.2629917363195909</v>
       </c>
       <c r="C68">
-        <v>-9.068669228731132</v>
+        <v>-9.916872916700445</v>
       </c>
       <c r="D68">
-        <v>28.66973077126887</v>
+        <v>28.41892708329956</v>
       </c>
       <c r="E68">
-        <v>35.3884</v>
+        <v>35.9858</v>
       </c>
       <c r="F68">
-        <v>39.4284</v>
+        <v>40.0258</v>
       </c>
       <c r="G68">
         <v>1.69</v>
@@ -6991,37 +6991,37 @@
         <v>3.52</v>
       </c>
       <c r="M68">
-        <v>9.297216720000002</v>
+        <v>9.438083640000002</v>
       </c>
       <c r="N68">
-        <v>-5.777216720000002</v>
+        <v>-5.918083640000003</v>
       </c>
       <c r="O68">
-        <v>-1.155443344</v>
+        <v>-1.183616728000001</v>
       </c>
       <c r="P68">
-        <v>-4.621773376000002</v>
+        <v>-4.734466912000002</v>
       </c>
       <c r="Q68">
-        <v>-4.961773376000002</v>
+        <v>-5.074466912000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3448474570064576</v>
+        <v>0.3539095011581684</v>
       </c>
       <c r="T68">
-        <v>4.626169051401734</v>
+        <v>4.766355992353302</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07572158649217763</v>
+        <v>0.07459141355945854</v>
       </c>
       <c r="W68">
-        <v>0.2179448499051445</v>
+        <v>0.2182113446826797</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3786079324608881</v>
+        <v>0.3729570677972927</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2629917363195909</v>
+        <v>0.264891736319591</v>
       </c>
       <c r="C69">
-        <v>-9.916872916700445</v>
+        <v>-10.76072658202494</v>
       </c>
       <c r="D69">
-        <v>28.41892708329956</v>
+        <v>28.17247341797507</v>
       </c>
       <c r="E69">
-        <v>35.9858</v>
+        <v>36.58320000000001</v>
       </c>
       <c r="F69">
-        <v>40.0258</v>
+        <v>40.6232</v>
       </c>
       <c r="G69">
         <v>1.69</v>
@@ -7073,37 +7073,37 @@
         <v>3.52</v>
       </c>
       <c r="M69">
-        <v>9.438083640000002</v>
+        <v>9.578950560000001</v>
       </c>
       <c r="N69">
-        <v>-5.918083640000003</v>
+        <v>-6.058950560000001</v>
       </c>
       <c r="O69">
-        <v>-1.183616728000001</v>
+        <v>-1.211790112</v>
       </c>
       <c r="P69">
-        <v>-4.734466912000002</v>
+        <v>-4.847160448000001</v>
       </c>
       <c r="Q69">
-        <v>-5.074466912000002</v>
+        <v>-5.187160448000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3539095011581684</v>
+        <v>0.3635379230693613</v>
       </c>
       <c r="T69">
-        <v>4.766355992353302</v>
+        <v>4.915304617114344</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07459141355945854</v>
+        <v>0.07349448100711357</v>
       </c>
       <c r="W69">
-        <v>0.2182113446826797</v>
+        <v>0.2184700013785226</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3729570677972927</v>
+        <v>0.3674724050355678</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.264891736319591</v>
+        <v>0.266791736319591</v>
       </c>
       <c r="C70">
-        <v>-10.76072658202494</v>
+        <v>-11.60034242405418</v>
       </c>
       <c r="D70">
-        <v>28.17247341797507</v>
+        <v>27.93025757594583</v>
       </c>
       <c r="E70">
-        <v>36.58320000000001</v>
+        <v>37.18060000000001</v>
       </c>
       <c r="F70">
-        <v>40.6232</v>
+        <v>41.2206</v>
       </c>
       <c r="G70">
         <v>1.69</v>
@@ -7155,37 +7155,37 @@
         <v>3.52</v>
       </c>
       <c r="M70">
-        <v>9.578950560000001</v>
+        <v>9.719817480000001</v>
       </c>
       <c r="N70">
-        <v>-6.058950560000001</v>
+        <v>-6.199817480000002</v>
       </c>
       <c r="O70">
-        <v>-1.211790112</v>
+        <v>-1.239963496000001</v>
       </c>
       <c r="P70">
-        <v>-4.847160448000001</v>
+        <v>-4.959853984000001</v>
       </c>
       <c r="Q70">
-        <v>-5.187160448000001</v>
+        <v>-5.299853984000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3635379230693613</v>
+        <v>0.3737875334909536</v>
       </c>
       <c r="T70">
-        <v>4.915304617114344</v>
+        <v>5.073862830569644</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07349448100711357</v>
+        <v>0.07242934360121338</v>
       </c>
       <c r="W70">
-        <v>0.2184700013785226</v>
+        <v>0.2187211607788339</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3674724050355678</v>
+        <v>0.3621467180060668</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.266791736319591</v>
+        <v>0.2686917363195909</v>
       </c>
       <c r="C71">
-        <v>-11.60034242405418</v>
+        <v>-12.43582881644606</v>
       </c>
       <c r="D71">
-        <v>27.93025757594583</v>
+        <v>27.69217118355394</v>
       </c>
       <c r="E71">
-        <v>37.18060000000001</v>
+        <v>37.77800000000001</v>
       </c>
       <c r="F71">
-        <v>41.2206</v>
+        <v>41.818</v>
       </c>
       <c r="G71">
         <v>1.69</v>
@@ -7237,37 +7237,37 @@
         <v>3.52</v>
       </c>
       <c r="M71">
-        <v>9.719817480000001</v>
+        <v>9.860684400000002</v>
       </c>
       <c r="N71">
-        <v>-6.199817480000002</v>
+        <v>-6.340684400000002</v>
       </c>
       <c r="O71">
-        <v>-1.239963496000001</v>
+        <v>-1.268136880000001</v>
       </c>
       <c r="P71">
-        <v>-4.959853984000001</v>
+        <v>-5.072547520000002</v>
       </c>
       <c r="Q71">
-        <v>-5.299853984000001</v>
+        <v>-5.412547520000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3737875334909536</v>
+        <v>0.3847204512739852</v>
       </c>
       <c r="T71">
-        <v>5.073862830569644</v>
+        <v>5.242991591588631</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07242934360121338</v>
+        <v>0.07139463869262462</v>
       </c>
       <c r="W71">
-        <v>0.2187211607788339</v>
+        <v>0.2189651441962791</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3621467180060668</v>
+        <v>0.356973193463123</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2686917363195909</v>
+        <v>0.270591736319591</v>
       </c>
       <c r="C72">
-        <v>-12.43582881644606</v>
+        <v>-13.26729046884573</v>
       </c>
       <c r="D72">
-        <v>27.69217118355394</v>
+        <v>27.45810953115427</v>
       </c>
       <c r="E72">
-        <v>37.77800000000001</v>
+        <v>38.37540000000001</v>
       </c>
       <c r="F72">
-        <v>41.818</v>
+        <v>42.41540000000001</v>
       </c>
       <c r="G72">
         <v>1.69</v>
@@ -7319,37 +7319,37 @@
         <v>3.52</v>
       </c>
       <c r="M72">
-        <v>9.860684400000002</v>
+        <v>10.00155132</v>
       </c>
       <c r="N72">
-        <v>-6.340684400000002</v>
+        <v>-6.481551320000001</v>
       </c>
       <c r="O72">
-        <v>-1.268136880000001</v>
+        <v>-1.296310264</v>
       </c>
       <c r="P72">
-        <v>-5.072547520000002</v>
+        <v>-5.185241056000001</v>
       </c>
       <c r="Q72">
-        <v>-5.412547520000002</v>
+        <v>-5.525241056</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3847204512739852</v>
+        <v>0.3964073633868814</v>
       </c>
       <c r="T72">
-        <v>5.242991591588631</v>
+        <v>5.423784405091689</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07139463869262462</v>
+        <v>0.07038908040117919</v>
       </c>
       <c r="W72">
-        <v>0.2189651441962791</v>
+        <v>0.219202254841402</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.356973193463123</v>
+        <v>0.351945402005896</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.270591736319591</v>
+        <v>0.2724917363195909</v>
       </c>
       <c r="C73">
-        <v>-13.26729046884572</v>
+        <v>-14.09482858043371</v>
       </c>
       <c r="D73">
-        <v>27.45810953115427</v>
+        <v>27.22797141956629</v>
       </c>
       <c r="E73">
-        <v>38.3754</v>
+        <v>38.9728</v>
       </c>
       <c r="F73">
-        <v>42.4154</v>
+        <v>43.0128</v>
       </c>
       <c r="G73">
         <v>1.69</v>
@@ -7401,37 +7401,37 @@
         <v>3.52</v>
       </c>
       <c r="M73">
-        <v>10.00155132</v>
+        <v>10.14241824</v>
       </c>
       <c r="N73">
-        <v>-6.481551320000001</v>
+        <v>-6.62241824</v>
       </c>
       <c r="O73">
-        <v>-1.296310264</v>
+        <v>-1.324483648</v>
       </c>
       <c r="P73">
-        <v>-5.185241056000001</v>
+        <v>-5.297934592</v>
       </c>
       <c r="Q73">
-        <v>-5.525241056</v>
+        <v>-5.637934592</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3964073633868813</v>
+        <v>0.4089290549364127</v>
       </c>
       <c r="T73">
-        <v>5.423784405091688</v>
+        <v>5.617490990987819</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07038908040117919</v>
+        <v>0.06941145428449617</v>
       </c>
       <c r="W73">
-        <v>0.219202254841402</v>
+        <v>0.2194327790797158</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.351945402005896</v>
+        <v>0.3470572714224808</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2724917363195909</v>
+        <v>0.274391736319591</v>
       </c>
       <c r="C74">
-        <v>-14.09482858043371</v>
+        <v>-14.91854098581677</v>
       </c>
       <c r="D74">
-        <v>27.22797141956629</v>
+        <v>27.00165901418323</v>
       </c>
       <c r="E74">
-        <v>38.9728</v>
+        <v>39.5702</v>
       </c>
       <c r="F74">
-        <v>43.0128</v>
+        <v>43.6102</v>
       </c>
       <c r="G74">
         <v>1.69</v>
@@ -7483,37 +7483,37 @@
         <v>3.52</v>
       </c>
       <c r="M74">
-        <v>10.14241824</v>
+        <v>10.28328516</v>
       </c>
       <c r="N74">
-        <v>-6.62241824</v>
+        <v>-6.763285160000001</v>
       </c>
       <c r="O74">
-        <v>-1.324483648</v>
+        <v>-1.352657032</v>
       </c>
       <c r="P74">
-        <v>-5.297934592</v>
+        <v>-5.410628128000001</v>
       </c>
       <c r="Q74">
-        <v>-5.637934592</v>
+        <v>-5.750628128000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4089290549364127</v>
+        <v>0.4223782791933169</v>
       </c>
       <c r="T74">
-        <v>5.617490990987819</v>
+        <v>5.825546212876256</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06941145428449617</v>
+        <v>0.06846061244498251</v>
       </c>
       <c r="W74">
-        <v>0.2194327790797158</v>
+        <v>0.2196569875854731</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3470572714224808</v>
+        <v>0.3423030622249125</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.274391736319591</v>
+        <v>0.2762917363195909</v>
       </c>
       <c r="C75">
-        <v>-14.91854098581677</v>
+        <v>-15.73852229370284</v>
       </c>
       <c r="D75">
-        <v>27.00165901418323</v>
+        <v>26.77907770629716</v>
       </c>
       <c r="E75">
-        <v>39.5702</v>
+        <v>40.1676</v>
       </c>
       <c r="F75">
-        <v>43.6102</v>
+        <v>44.2076</v>
       </c>
       <c r="G75">
         <v>1.69</v>
@@ -7565,37 +7565,37 @@
         <v>3.52</v>
       </c>
       <c r="M75">
-        <v>10.28328516</v>
+        <v>10.42415208</v>
       </c>
       <c r="N75">
-        <v>-6.763285160000001</v>
+        <v>-6.904152080000001</v>
       </c>
       <c r="O75">
-        <v>-1.352657032</v>
+        <v>-1.380830416</v>
       </c>
       <c r="P75">
-        <v>-5.410628128000001</v>
+        <v>-5.523321664000001</v>
       </c>
       <c r="Q75">
-        <v>-5.750628128000001</v>
+        <v>-5.863321664000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4223782791933169</v>
+        <v>0.4368620591622906</v>
       </c>
       <c r="T75">
-        <v>5.825546212876256</v>
+        <v>6.049605682602266</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06846061244498251</v>
+        <v>0.06753546903356382</v>
       </c>
       <c r="W75">
-        <v>0.2196569875854731</v>
+        <v>0.2198751364018857</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3423030622249125</v>
+        <v>0.3376773451678191</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2762917363195909</v>
+        <v>0.2781917363195909</v>
       </c>
       <c r="C76">
-        <v>-15.73852229370284</v>
+        <v>-16.55486401877345</v>
       </c>
       <c r="D76">
-        <v>26.77907770629716</v>
+        <v>26.56013598122655</v>
       </c>
       <c r="E76">
-        <v>40.1676</v>
+        <v>40.765</v>
       </c>
       <c r="F76">
-        <v>44.2076</v>
+        <v>44.805</v>
       </c>
       <c r="G76">
         <v>1.69</v>
@@ -7647,37 +7647,37 @@
         <v>3.52</v>
       </c>
       <c r="M76">
-        <v>10.42415208</v>
+        <v>10.565019</v>
       </c>
       <c r="N76">
-        <v>-6.904152080000001</v>
+        <v>-7.045019</v>
       </c>
       <c r="O76">
-        <v>-1.380830416</v>
+        <v>-1.4090038</v>
       </c>
       <c r="P76">
-        <v>-5.523321664000001</v>
+        <v>-5.6360152</v>
       </c>
       <c r="Q76">
-        <v>-5.863321664000001</v>
+        <v>-5.9760152</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4368620591622906</v>
+        <v>0.4525045415287823</v>
       </c>
       <c r="T76">
-        <v>6.049605682602266</v>
+        <v>6.291589909906357</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06753546903356382</v>
+        <v>0.06663499611311632</v>
       </c>
       <c r="W76">
-        <v>0.2198751364018857</v>
+        <v>0.2200874679165272</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3376773451678191</v>
+        <v>0.3331749805655816</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2781917363195909</v>
+        <v>0.2800917363195909</v>
       </c>
       <c r="C77">
-        <v>-16.55486401877345</v>
+        <v>-17.3676547071394</v>
       </c>
       <c r="D77">
-        <v>26.56013598122655</v>
+        <v>26.3447452928606</v>
       </c>
       <c r="E77">
-        <v>40.765</v>
+        <v>41.3624</v>
       </c>
       <c r="F77">
-        <v>44.805</v>
+        <v>45.4024</v>
       </c>
       <c r="G77">
         <v>1.69</v>
@@ -7729,37 +7729,37 @@
         <v>3.52</v>
       </c>
       <c r="M77">
-        <v>10.565019</v>
+        <v>10.70588592</v>
       </c>
       <c r="N77">
-        <v>-7.045019</v>
+        <v>-7.18588592</v>
       </c>
       <c r="O77">
-        <v>-1.4090038</v>
+        <v>-1.437177184</v>
       </c>
       <c r="P77">
-        <v>-5.6360152</v>
+        <v>-5.748708736</v>
       </c>
       <c r="Q77">
-        <v>-5.9760152</v>
+        <v>-6.088708736</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4525045415287823</v>
+        <v>0.4694505640924815</v>
       </c>
       <c r="T77">
-        <v>6.291589909906357</v>
+        <v>6.553739489485789</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06663499611311632</v>
+        <v>0.06575821984847005</v>
       </c>
       <c r="W77">
-        <v>0.2200874679165272</v>
+        <v>0.2202942117597308</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3331749805655816</v>
+        <v>0.3287910992423502</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2800917363195909</v>
+        <v>0.281991736319591</v>
       </c>
       <c r="C78">
-        <v>-17.3676547071394</v>
+        <v>-18.17698005574138</v>
       </c>
       <c r="D78">
-        <v>26.3447452928606</v>
+        <v>26.13281994425862</v>
       </c>
       <c r="E78">
-        <v>41.3624</v>
+        <v>41.9598</v>
       </c>
       <c r="F78">
-        <v>45.4024</v>
+        <v>45.9998</v>
       </c>
       <c r="G78">
         <v>1.69</v>
@@ -7811,37 +7811,37 @@
         <v>3.52</v>
       </c>
       <c r="M78">
-        <v>10.70588592</v>
+        <v>10.84675284</v>
       </c>
       <c r="N78">
-        <v>-7.18588592</v>
+        <v>-7.326752840000001</v>
       </c>
       <c r="O78">
-        <v>-1.437177184</v>
+        <v>-1.465350568</v>
       </c>
       <c r="P78">
-        <v>-5.748708736</v>
+        <v>-5.861402272000001</v>
       </c>
       <c r="Q78">
-        <v>-6.088708736</v>
+        <v>-6.201402272000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4694505640924815</v>
+        <v>0.487870153835633</v>
       </c>
       <c r="T78">
-        <v>6.553739489485789</v>
+        <v>6.838684684680824</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06575821984847005</v>
+        <v>0.06490421699329511</v>
       </c>
       <c r="W78">
-        <v>0.2202942117597308</v>
+        <v>0.220495585632981</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3287910992423502</v>
+        <v>0.3245210849664755</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.281991736319591</v>
+        <v>0.283891736319591</v>
       </c>
       <c r="C79">
-        <v>-18.17698005574138</v>
+        <v>-18.98292302603348</v>
       </c>
       <c r="D79">
-        <v>26.13281994425862</v>
+        <v>25.92427697396652</v>
       </c>
       <c r="E79">
-        <v>41.9598</v>
+        <v>42.5572</v>
       </c>
       <c r="F79">
-        <v>45.9998</v>
+        <v>46.5972</v>
       </c>
       <c r="G79">
         <v>1.69</v>
@@ -7893,37 +7893,37 @@
         <v>3.52</v>
       </c>
       <c r="M79">
-        <v>10.84675284</v>
+        <v>10.98761976</v>
       </c>
       <c r="N79">
-        <v>-7.326752840000001</v>
+        <v>-7.467619760000002</v>
       </c>
       <c r="O79">
-        <v>-1.465350568</v>
+        <v>-1.493523952</v>
       </c>
       <c r="P79">
-        <v>-5.861402272000001</v>
+        <v>-5.974095808000001</v>
       </c>
       <c r="Q79">
-        <v>-6.201402272000001</v>
+        <v>-6.314095808000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.487870153835633</v>
+        <v>0.5079642517372527</v>
       </c>
       <c r="T79">
-        <v>6.838684684680824</v>
+        <v>7.149533988529953</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06490421699329511</v>
+        <v>0.06407211164722722</v>
       </c>
       <c r="W79">
-        <v>0.220495585632981</v>
+        <v>0.2206917960735838</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3245210849664755</v>
+        <v>0.3203605582361361</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.283891736319591</v>
+        <v>0.2857917363195909</v>
       </c>
       <c r="C80">
-        <v>-18.98292302603348</v>
+        <v>-19.78556395226664</v>
       </c>
       <c r="D80">
-        <v>25.92427697396652</v>
+        <v>25.71903604773336</v>
       </c>
       <c r="E80">
-        <v>42.5572</v>
+        <v>43.1546</v>
       </c>
       <c r="F80">
-        <v>46.5972</v>
+        <v>47.1946</v>
       </c>
       <c r="G80">
         <v>1.69</v>
@@ -7975,37 +7975,37 @@
         <v>3.52</v>
       </c>
       <c r="M80">
-        <v>10.98761976</v>
+        <v>11.12848668</v>
       </c>
       <c r="N80">
-        <v>-7.467619760000002</v>
+        <v>-7.60848668</v>
       </c>
       <c r="O80">
-        <v>-1.493523952</v>
+        <v>-1.521697336</v>
       </c>
       <c r="P80">
-        <v>-5.974095808000001</v>
+        <v>-6.086789344</v>
       </c>
       <c r="Q80">
-        <v>-6.314095808000001</v>
+        <v>-6.426789344</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5079642517372527</v>
+        <v>0.5299720732485503</v>
       </c>
       <c r="T80">
-        <v>7.149533988529953</v>
+        <v>7.48998798798376</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06407211164722722</v>
+        <v>0.06326107225928765</v>
       </c>
       <c r="W80">
-        <v>0.2206917960735838</v>
+        <v>0.22088303916126</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3203605582361361</v>
+        <v>0.3163053612964382</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2857917363195909</v>
+        <v>0.2876917363195909</v>
       </c>
       <c r="C81">
-        <v>-19.78556395226664</v>
+        <v>-20.58498064466877</v>
       </c>
       <c r="D81">
-        <v>25.71903604773336</v>
+        <v>25.51701935533123</v>
       </c>
       <c r="E81">
-        <v>43.1546</v>
+        <v>43.752</v>
       </c>
       <c r="F81">
-        <v>47.1946</v>
+        <v>47.792</v>
       </c>
       <c r="G81">
         <v>1.69</v>
@@ -8057,37 +8057,37 @@
         <v>3.52</v>
       </c>
       <c r="M81">
-        <v>11.12848668</v>
+        <v>11.2693536</v>
       </c>
       <c r="N81">
-        <v>-7.60848668</v>
+        <v>-7.749353600000001</v>
       </c>
       <c r="O81">
-        <v>-1.521697336</v>
+        <v>-1.54987072</v>
       </c>
       <c r="P81">
-        <v>-6.086789344</v>
+        <v>-6.199482880000001</v>
       </c>
       <c r="Q81">
-        <v>-6.426789344</v>
+        <v>-6.53948288</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5299720732485503</v>
+        <v>0.5541806769109779</v>
       </c>
       <c r="T81">
-        <v>7.48998798798376</v>
+        <v>7.864487387382948</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06326107225928765</v>
+        <v>0.06247030885604654</v>
       </c>
       <c r="W81">
-        <v>0.22088303916126</v>
+        <v>0.2210695011717442</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3163053612964382</v>
+        <v>0.3123515442802327</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2876917363195909</v>
+        <v>0.289591736319591</v>
       </c>
       <c r="C82">
-        <v>-20.58498064466877</v>
+        <v>-21.38124848780014</v>
       </c>
       <c r="D82">
-        <v>25.51701935533123</v>
+        <v>25.31815151219986</v>
       </c>
       <c r="E82">
-        <v>43.752</v>
+        <v>44.3494</v>
       </c>
       <c r="F82">
-        <v>47.792</v>
+        <v>48.3894</v>
       </c>
       <c r="G82">
         <v>1.69</v>
@@ -8139,37 +8139,37 @@
         <v>3.52</v>
       </c>
       <c r="M82">
-        <v>11.2693536</v>
+        <v>11.41022052</v>
       </c>
       <c r="N82">
-        <v>-7.749353600000001</v>
+        <v>-7.890220520000002</v>
       </c>
       <c r="O82">
-        <v>-1.54987072</v>
+        <v>-1.578044104</v>
       </c>
       <c r="P82">
-        <v>-6.199482880000001</v>
+        <v>-6.312176416000002</v>
       </c>
       <c r="Q82">
-        <v>-6.53948288</v>
+        <v>-6.652176416000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5541806769109779</v>
+        <v>0.5809375546431347</v>
       </c>
       <c r="T82">
-        <v>7.864487387382948</v>
+        <v>8.278407776192578</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06247030885604654</v>
+        <v>0.06169907047510769</v>
       </c>
       <c r="W82">
-        <v>0.2210695011717442</v>
+        <v>0.2212513591819696</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3123515442802327</v>
+        <v>0.3084953523755384</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.289591736319591</v>
+        <v>0.291491736319591</v>
       </c>
       <c r="C83">
-        <v>-21.38124848780014</v>
+        <v>-22.17444053434504</v>
       </c>
       <c r="D83">
-        <v>25.31815151219986</v>
+        <v>25.12235946565496</v>
       </c>
       <c r="E83">
-        <v>44.3494</v>
+        <v>44.9468</v>
       </c>
       <c r="F83">
-        <v>48.3894</v>
+        <v>48.9868</v>
       </c>
       <c r="G83">
         <v>1.69</v>
@@ -8221,37 +8221,37 @@
         <v>3.52</v>
       </c>
       <c r="M83">
-        <v>11.41022052</v>
+        <v>11.55108744</v>
       </c>
       <c r="N83">
-        <v>-7.890220520000002</v>
+        <v>-8.031087440000002</v>
       </c>
       <c r="O83">
-        <v>-1.578044104</v>
+        <v>-1.606217488</v>
       </c>
       <c r="P83">
-        <v>-6.312176416000002</v>
+        <v>-6.424869952000002</v>
       </c>
       <c r="Q83">
-        <v>-6.652176416000001</v>
+        <v>-6.764869952000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5809375546431347</v>
+        <v>0.6106674187899755</v>
       </c>
       <c r="T83">
-        <v>8.278407776192578</v>
+        <v>8.738319319314389</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06169907047510769</v>
+        <v>0.06094664278638687</v>
       </c>
       <c r="W83">
-        <v>0.2212513591819696</v>
+        <v>0.22142878163097</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3084953523755384</v>
+        <v>0.3047332139319343</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.291491736319591</v>
+        <v>0.293391736319591</v>
       </c>
       <c r="C84">
-        <v>-22.17444053434504</v>
+        <v>-22.96462759458493</v>
       </c>
       <c r="D84">
-        <v>25.12235946565496</v>
+        <v>24.92957240541507</v>
       </c>
       <c r="E84">
-        <v>44.9468</v>
+        <v>45.5442</v>
       </c>
       <c r="F84">
-        <v>48.9868</v>
+        <v>49.5842</v>
       </c>
       <c r="G84">
         <v>1.69</v>
@@ -8303,37 +8303,37 @@
         <v>3.52</v>
       </c>
       <c r="M84">
-        <v>11.55108744</v>
+        <v>11.69195436</v>
       </c>
       <c r="N84">
-        <v>-8.031087440000002</v>
+        <v>-8.171954360000001</v>
       </c>
       <c r="O84">
-        <v>-1.606217488</v>
+        <v>-1.634390872</v>
       </c>
       <c r="P84">
-        <v>-6.424869952000002</v>
+        <v>-6.537563488000001</v>
       </c>
       <c r="Q84">
-        <v>-6.764869952000002</v>
+        <v>-6.877563488000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6106674187899755</v>
+        <v>0.6438949140129153</v>
       </c>
       <c r="T84">
-        <v>8.738319319314389</v>
+        <v>9.252338102803471</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06094664278638687</v>
+        <v>0.06021234588534607</v>
       </c>
       <c r="W84">
-        <v>0.22142878163097</v>
+        <v>0.2216019288402354</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3047332139319343</v>
+        <v>0.3010617294267303</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.293391736319591</v>
+        <v>0.295291736319591</v>
       </c>
       <c r="C85">
-        <v>-22.96462759458493</v>
+        <v>-23.75187832178342</v>
       </c>
       <c r="D85">
-        <v>24.92957240541507</v>
+        <v>24.73972167821658</v>
       </c>
       <c r="E85">
-        <v>45.5442</v>
+        <v>46.1416</v>
       </c>
       <c r="F85">
-        <v>49.5842</v>
+        <v>50.1816</v>
       </c>
       <c r="G85">
         <v>1.69</v>
@@ -8385,37 +8385,37 @@
         <v>3.52</v>
       </c>
       <c r="M85">
-        <v>11.69195436</v>
+        <v>11.83282128</v>
       </c>
       <c r="N85">
-        <v>-8.171954360000001</v>
+        <v>-8.312821280000001</v>
       </c>
       <c r="O85">
-        <v>-1.634390872</v>
+        <v>-1.662564256</v>
       </c>
       <c r="P85">
-        <v>-6.537563488000001</v>
+        <v>-6.650257024000001</v>
       </c>
       <c r="Q85">
-        <v>-6.877563488000001</v>
+        <v>-6.990257024000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6438949140129153</v>
+        <v>0.6812758461387226</v>
       </c>
       <c r="T85">
-        <v>9.252338102803471</v>
+        <v>9.830609234228689</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06021234588534607</v>
+        <v>0.05949553224385384</v>
       </c>
       <c r="W85">
-        <v>0.2216019288402354</v>
+        <v>0.2217709534968993</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3010617294267303</v>
+        <v>0.2974776612192692</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2952917363195909</v>
+        <v>0.2971917363195909</v>
       </c>
       <c r="C86">
-        <v>-23.75187832178342</v>
+        <v>-24.53625929369911</v>
       </c>
       <c r="D86">
-        <v>24.73972167821659</v>
+        <v>24.55274070630089</v>
       </c>
       <c r="E86">
-        <v>46.1416</v>
+        <v>46.739</v>
       </c>
       <c r="F86">
-        <v>50.1816</v>
+        <v>50.779</v>
       </c>
       <c r="G86">
         <v>1.69</v>
@@ -8467,37 +8467,37 @@
         <v>3.52</v>
       </c>
       <c r="M86">
-        <v>11.83282128</v>
+        <v>11.9736882</v>
       </c>
       <c r="N86">
-        <v>-8.312821280000001</v>
+        <v>-8.453688200000002</v>
       </c>
       <c r="O86">
-        <v>-1.662564256</v>
+        <v>-1.69073764</v>
       </c>
       <c r="P86">
-        <v>-6.650257024000001</v>
+        <v>-6.762950560000002</v>
       </c>
       <c r="Q86">
-        <v>-6.990257024000001</v>
+        <v>-7.102950560000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6812758461387222</v>
+        <v>0.7236409025479703</v>
       </c>
       <c r="T86">
-        <v>9.830609234228682</v>
+        <v>10.48598318317726</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05949553224385384</v>
+        <v>0.05879558480569086</v>
       </c>
       <c r="W86">
-        <v>0.2217709534968993</v>
+        <v>0.2219360011028181</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2974776612192692</v>
+        <v>0.2939779240284542</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2971917363195909</v>
+        <v>0.299091736319591</v>
       </c>
       <c r="C87">
-        <v>-24.53625929369911</v>
+        <v>-25.31783509042985</v>
       </c>
       <c r="D87">
-        <v>24.55274070630089</v>
+        <v>24.36856490957015</v>
       </c>
       <c r="E87">
-        <v>46.739</v>
+        <v>47.3364</v>
       </c>
       <c r="F87">
-        <v>50.779</v>
+        <v>51.3764</v>
       </c>
       <c r="G87">
         <v>1.69</v>
@@ -8549,37 +8549,37 @@
         <v>3.52</v>
       </c>
       <c r="M87">
-        <v>11.9736882</v>
+        <v>12.11455512</v>
       </c>
       <c r="N87">
-        <v>-8.453688200000002</v>
+        <v>-8.594555120000003</v>
       </c>
       <c r="O87">
-        <v>-1.69073764</v>
+        <v>-1.718911024000001</v>
       </c>
       <c r="P87">
-        <v>-6.762950560000002</v>
+        <v>-6.875644096000002</v>
       </c>
       <c r="Q87">
-        <v>-7.102950560000002</v>
+        <v>-7.215644096000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7236409025479703</v>
+        <v>0.7720581098728254</v>
       </c>
       <c r="T87">
-        <v>10.48598318317726</v>
+        <v>11.23498198197564</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05879558480569086</v>
+        <v>0.05811191521492701</v>
       </c>
       <c r="W87">
-        <v>0.2219360011028181</v>
+        <v>0.2220972103923202</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2939779240284542</v>
+        <v>0.290559576074635</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.299091736319591</v>
+        <v>0.3009917363195909</v>
       </c>
       <c r="C88">
-        <v>-25.31783509042985</v>
+        <v>-26.09666836877942</v>
       </c>
       <c r="D88">
-        <v>24.36856490957015</v>
+        <v>24.18713163122058</v>
       </c>
       <c r="E88">
-        <v>47.3364</v>
+        <v>47.93380000000001</v>
       </c>
       <c r="F88">
-        <v>51.3764</v>
+        <v>51.9738</v>
       </c>
       <c r="G88">
         <v>1.69</v>
@@ -8631,37 +8631,37 @@
         <v>3.52</v>
       </c>
       <c r="M88">
-        <v>12.11455512</v>
+        <v>12.25542204</v>
       </c>
       <c r="N88">
-        <v>-8.594555120000003</v>
+        <v>-8.735422040000001</v>
       </c>
       <c r="O88">
-        <v>-1.718911024000001</v>
+        <v>-1.747084408</v>
       </c>
       <c r="P88">
-        <v>-6.875644096000002</v>
+        <v>-6.988337632000001</v>
       </c>
       <c r="Q88">
-        <v>-7.215644096000002</v>
+        <v>-7.328337632000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7720581098728254</v>
+        <v>0.8279241183245811</v>
       </c>
       <c r="T88">
-        <v>11.23498198197564</v>
+        <v>12.09921136520453</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05811191521492701</v>
+        <v>0.05744396216647958</v>
       </c>
       <c r="W88">
-        <v>0.2220972103923202</v>
+        <v>0.2222547137211441</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.290559576074635</v>
+        <v>0.2872198108323979</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3009917363195909</v>
+        <v>0.3028917363195909</v>
       </c>
       <c r="C89">
-        <v>-26.09666836877942</v>
+        <v>-26.87281993332676</v>
       </c>
       <c r="D89">
-        <v>24.18713163122058</v>
+        <v>24.00838006667324</v>
       </c>
       <c r="E89">
-        <v>47.93380000000001</v>
+        <v>48.53120000000001</v>
       </c>
       <c r="F89">
-        <v>51.9738</v>
+        <v>52.5712</v>
       </c>
       <c r="G89">
         <v>1.69</v>
@@ -8713,37 +8713,37 @@
         <v>3.52</v>
       </c>
       <c r="M89">
-        <v>12.25542204</v>
+        <v>12.39628896</v>
       </c>
       <c r="N89">
-        <v>-8.735422040000001</v>
+        <v>-8.876288960000002</v>
       </c>
       <c r="O89">
-        <v>-1.747084408</v>
+        <v>-1.775257792000001</v>
       </c>
       <c r="P89">
-        <v>-6.988337632000001</v>
+        <v>-7.101031168000001</v>
       </c>
       <c r="Q89">
-        <v>-7.328337632000001</v>
+        <v>-7.441031168000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8279241183245811</v>
+        <v>0.893101128184963</v>
       </c>
       <c r="T89">
-        <v>12.09921136520453</v>
+        <v>13.10747897897158</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05744396216647958</v>
+        <v>0.05679118986913322</v>
       </c>
       <c r="W89">
-        <v>0.2222547137211441</v>
+        <v>0.2224086374288584</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2872198108323979</v>
+        <v>0.283955949345666</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3028917363195909</v>
+        <v>0.3047917363195909</v>
       </c>
       <c r="C90">
-        <v>-26.87281993332676</v>
+        <v>-27.64634880436684</v>
       </c>
       <c r="D90">
-        <v>24.00838006667324</v>
+        <v>23.83225119563317</v>
       </c>
       <c r="E90">
-        <v>48.53120000000001</v>
+        <v>49.12860000000001</v>
       </c>
       <c r="F90">
-        <v>52.5712</v>
+        <v>53.1686</v>
       </c>
       <c r="G90">
         <v>1.69</v>
@@ -8795,37 +8795,37 @@
         <v>3.52</v>
       </c>
       <c r="M90">
-        <v>12.39628896</v>
+        <v>12.53715588</v>
       </c>
       <c r="N90">
-        <v>-8.876288960000002</v>
+        <v>-9.017155880000002</v>
       </c>
       <c r="O90">
-        <v>-1.775257792000001</v>
+        <v>-1.803431176000001</v>
       </c>
       <c r="P90">
-        <v>-7.101031168000001</v>
+        <v>-7.213724704000002</v>
       </c>
       <c r="Q90">
-        <v>-7.441031168000001</v>
+        <v>-7.553724704000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.893101128184963</v>
+        <v>0.9701285034745053</v>
       </c>
       <c r="T90">
-        <v>13.10747897897158</v>
+        <v>14.29906797705991</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05679118986913322</v>
+        <v>0.05615308661217666</v>
       </c>
       <c r="W90">
-        <v>0.2224086374288584</v>
+        <v>0.2225591021768487</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.283955949345666</v>
+        <v>0.2807654330608833</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3047917363195909</v>
+        <v>0.306691736319591</v>
       </c>
       <c r="C91">
-        <v>-27.64634880436684</v>
+        <v>-28.41731228288283</v>
       </c>
       <c r="D91">
-        <v>23.83225119563317</v>
+        <v>23.65868771711717</v>
       </c>
       <c r="E91">
-        <v>49.12860000000001</v>
+        <v>49.72600000000001</v>
       </c>
       <c r="F91">
-        <v>53.1686</v>
+        <v>53.76600000000001</v>
       </c>
       <c r="G91">
         <v>1.69</v>
@@ -8877,37 +8877,37 @@
         <v>3.52</v>
       </c>
       <c r="M91">
-        <v>12.53715588</v>
+        <v>12.6780228</v>
       </c>
       <c r="N91">
-        <v>-9.017155880000002</v>
+        <v>-9.158022800000003</v>
       </c>
       <c r="O91">
-        <v>-1.803431176000001</v>
+        <v>-1.831604560000001</v>
       </c>
       <c r="P91">
-        <v>-7.213724704000002</v>
+        <v>-7.326418240000002</v>
       </c>
       <c r="Q91">
-        <v>-7.553724704000002</v>
+        <v>-7.666418240000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9701285034745053</v>
+        <v>1.062561353821956</v>
       </c>
       <c r="T91">
-        <v>14.29906797705991</v>
+        <v>15.7289747747659</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05615308661217666</v>
+        <v>0.05552916342759692</v>
       </c>
       <c r="W91">
-        <v>0.2225591021768487</v>
+        <v>0.2227062232637727</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2807654330608833</v>
+        <v>0.2776458171379845</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.306691736319591</v>
+        <v>0.308591736319591</v>
       </c>
       <c r="C92">
-        <v>-28.41731228288283</v>
+        <v>-29.18576601269972</v>
       </c>
       <c r="D92">
-        <v>23.65868771711717</v>
+        <v>23.48763398730028</v>
       </c>
       <c r="E92">
-        <v>49.72600000000001</v>
+        <v>50.32340000000001</v>
       </c>
       <c r="F92">
-        <v>53.76600000000001</v>
+        <v>54.36340000000001</v>
       </c>
       <c r="G92">
         <v>1.69</v>
@@ -8959,37 +8959,37 @@
         <v>3.52</v>
       </c>
       <c r="M92">
-        <v>12.6780228</v>
+        <v>12.81888972</v>
       </c>
       <c r="N92">
-        <v>-9.158022800000003</v>
+        <v>-9.298889720000002</v>
       </c>
       <c r="O92">
-        <v>-1.831604560000001</v>
+        <v>-1.859777944</v>
       </c>
       <c r="P92">
-        <v>-7.326418240000002</v>
+        <v>-7.439111776000002</v>
       </c>
       <c r="Q92">
-        <v>-7.666418240000002</v>
+        <v>-7.779111776000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.062561353821956</v>
+        <v>1.175534837579951</v>
       </c>
       <c r="T92">
-        <v>15.7289747747659</v>
+        <v>17.47663863862878</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05552916342759692</v>
+        <v>0.05491895284048048</v>
       </c>
       <c r="W92">
-        <v>0.2227062232637727</v>
+        <v>0.2228501109202147</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2776458171379845</v>
+        <v>0.2745947642024024</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.308591736319591</v>
+        <v>0.310491736319591</v>
       </c>
       <c r="C93">
-        <v>-29.18576601269972</v>
+        <v>-29.95176403996109</v>
       </c>
       <c r="D93">
-        <v>23.48763398730028</v>
+        <v>23.31903596003891</v>
       </c>
       <c r="E93">
-        <v>50.32340000000001</v>
+        <v>50.92080000000001</v>
       </c>
       <c r="F93">
-        <v>54.36340000000001</v>
+        <v>54.96080000000001</v>
       </c>
       <c r="G93">
         <v>1.69</v>
@@ -9041,37 +9041,37 @@
         <v>3.52</v>
       </c>
       <c r="M93">
-        <v>12.81888972</v>
+        <v>12.95975664</v>
       </c>
       <c r="N93">
-        <v>-9.298889720000002</v>
+        <v>-9.439756640000002</v>
       </c>
       <c r="O93">
-        <v>-1.859777944</v>
+        <v>-1.887951328000001</v>
       </c>
       <c r="P93">
-        <v>-7.439111776000002</v>
+        <v>-7.551805312000002</v>
       </c>
       <c r="Q93">
-        <v>-7.779111776000001</v>
+        <v>-7.891805312000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.175534837579951</v>
+        <v>1.316751692277445</v>
       </c>
       <c r="T93">
-        <v>17.47663863862878</v>
+        <v>19.66121846845738</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05491895284048048</v>
+        <v>0.05432200770091004</v>
       </c>
       <c r="W93">
-        <v>0.2228501109202147</v>
+        <v>0.2229908705841254</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2745947642024024</v>
+        <v>0.2716100385045501</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.310491736319591</v>
+        <v>0.3123917363195909</v>
       </c>
       <c r="C94">
-        <v>-29.95176403996109</v>
+        <v>-30.7153588700625</v>
       </c>
       <c r="D94">
-        <v>23.31903596003891</v>
+        <v>23.1528411299375</v>
       </c>
       <c r="E94">
-        <v>50.92080000000001</v>
+        <v>51.51820000000001</v>
       </c>
       <c r="F94">
-        <v>54.96080000000001</v>
+        <v>55.55820000000001</v>
       </c>
       <c r="G94">
         <v>1.69</v>
@@ -9123,37 +9123,37 @@
         <v>3.52</v>
       </c>
       <c r="M94">
-        <v>12.95975664</v>
+        <v>13.10062356</v>
       </c>
       <c r="N94">
-        <v>-9.439756640000002</v>
+        <v>-9.580623560000003</v>
       </c>
       <c r="O94">
-        <v>-1.887951328000001</v>
+        <v>-1.916124712000001</v>
       </c>
       <c r="P94">
-        <v>-7.551805312000002</v>
+        <v>-7.664498848000003</v>
       </c>
       <c r="Q94">
-        <v>-7.891805312000002</v>
+        <v>-8.004498848000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.316751692277445</v>
+        <v>1.498316219745652</v>
       </c>
       <c r="T94">
-        <v>19.66121846845738</v>
+        <v>22.46996396395129</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05432200770091004</v>
+        <v>0.05373790009122283</v>
       </c>
       <c r="W94">
-        <v>0.2229908705841254</v>
+        <v>0.2231286031584897</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2716100385045501</v>
+        <v>0.2686895004561141</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3123917363195909</v>
+        <v>0.314291736319591</v>
       </c>
       <c r="C95">
-        <v>-30.7153588700625</v>
+        <v>-31.47660152216751</v>
       </c>
       <c r="D95">
-        <v>23.1528411299375</v>
+        <v>22.98899847783249</v>
       </c>
       <c r="E95">
-        <v>51.51820000000001</v>
+        <v>52.11560000000001</v>
       </c>
       <c r="F95">
-        <v>55.55820000000001</v>
+        <v>56.15560000000001</v>
       </c>
       <c r="G95">
         <v>1.69</v>
@@ -9205,37 +9205,37 @@
         <v>3.52</v>
       </c>
       <c r="M95">
-        <v>13.10062356</v>
+        <v>13.24149048</v>
       </c>
       <c r="N95">
-        <v>-9.580623560000003</v>
+        <v>-9.721490480000002</v>
       </c>
       <c r="O95">
-        <v>-1.916124712000001</v>
+        <v>-1.944298096</v>
       </c>
       <c r="P95">
-        <v>-7.664498848000003</v>
+        <v>-7.777192384000001</v>
       </c>
       <c r="Q95">
-        <v>-8.004498848000003</v>
+        <v>-8.117192384000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.498316219745652</v>
+        <v>1.740402256369928</v>
       </c>
       <c r="T95">
-        <v>22.46996396395129</v>
+        <v>26.21495795794318</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05373790009122283</v>
+        <v>0.05316622030301833</v>
       </c>
       <c r="W95">
-        <v>0.2231286031584897</v>
+        <v>0.2232634052525483</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2686895004561141</v>
+        <v>0.2658311015150916</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.314291736319591</v>
+        <v>0.316191736319591</v>
       </c>
       <c r="C96">
-        <v>-31.47660152216751</v>
+        <v>-32.2355415814253</v>
       </c>
       <c r="D96">
-        <v>22.98899847783249</v>
+        <v>22.82745841857471</v>
       </c>
       <c r="E96">
-        <v>52.11560000000001</v>
+        <v>52.71300000000001</v>
       </c>
       <c r="F96">
-        <v>56.15560000000001</v>
+        <v>56.75300000000001</v>
       </c>
       <c r="G96">
         <v>1.69</v>
@@ -9287,37 +9287,37 @@
         <v>3.52</v>
       </c>
       <c r="M96">
-        <v>13.24149048</v>
+        <v>13.3823574</v>
       </c>
       <c r="N96">
-        <v>-9.721490480000002</v>
+        <v>-9.862357400000002</v>
       </c>
       <c r="O96">
-        <v>-1.944298096</v>
+        <v>-1.97247148</v>
       </c>
       <c r="P96">
-        <v>-7.777192384000001</v>
+        <v>-7.889885920000002</v>
       </c>
       <c r="Q96">
-        <v>-8.117192384000001</v>
+        <v>-8.229885920000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.740402256369928</v>
+        <v>2.079322707643914</v>
       </c>
       <c r="T96">
-        <v>26.21495795794318</v>
+        <v>31.45794954953184</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05316622030301833</v>
+        <v>0.05260657587877603</v>
       </c>
       <c r="W96">
-        <v>0.2232634052525483</v>
+        <v>0.2233953694077846</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2658311015150916</v>
+        <v>0.2630328793938801</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.316191736319591</v>
+        <v>0.318091736319591</v>
       </c>
       <c r="C97">
-        <v>-32.2355415814253</v>
+        <v>-32.99222724900203</v>
       </c>
       <c r="D97">
-        <v>22.82745841857471</v>
+        <v>22.66817275099798</v>
       </c>
       <c r="E97">
-        <v>52.71300000000001</v>
+        <v>53.31040000000001</v>
       </c>
       <c r="F97">
-        <v>56.75300000000001</v>
+        <v>57.35040000000001</v>
       </c>
       <c r="G97">
         <v>1.69</v>
@@ -9369,37 +9369,37 @@
         <v>3.52</v>
       </c>
       <c r="M97">
-        <v>13.3823574</v>
+        <v>13.52322432</v>
       </c>
       <c r="N97">
-        <v>-9.862357400000002</v>
+        <v>-10.00322432</v>
       </c>
       <c r="O97">
-        <v>-1.97247148</v>
+        <v>-2.000644864000001</v>
       </c>
       <c r="P97">
-        <v>-7.889885920000002</v>
+        <v>-8.002579456000003</v>
       </c>
       <c r="Q97">
-        <v>-8.229885920000001</v>
+        <v>-8.342579456000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.079322707643914</v>
+        <v>2.587703384554894</v>
       </c>
       <c r="T97">
-        <v>31.45794954953184</v>
+        <v>39.32243693691481</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05260657587877603</v>
+        <v>0.05205859071337211</v>
       </c>
       <c r="W97">
-        <v>0.2233953694077846</v>
+        <v>0.2235245843097869</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2630328793938801</v>
+        <v>0.2602929535668606</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3180917363195909</v>
+        <v>0.319991736319591</v>
       </c>
       <c r="C98">
-        <v>-32.99222724900201</v>
+        <v>-33.74670539003212</v>
       </c>
       <c r="D98">
-        <v>22.66817275099798</v>
+        <v>22.51109460996788</v>
       </c>
       <c r="E98">
-        <v>53.3104</v>
+        <v>53.9078</v>
       </c>
       <c r="F98">
-        <v>57.3504</v>
+        <v>57.9478</v>
       </c>
       <c r="G98">
         <v>1.69</v>
@@ -9451,37 +9451,37 @@
         <v>3.52</v>
       </c>
       <c r="M98">
-        <v>13.52322432</v>
+        <v>13.66409124</v>
       </c>
       <c r="N98">
-        <v>-10.00322432</v>
+        <v>-10.14409124</v>
       </c>
       <c r="O98">
-        <v>-2.000644864</v>
+        <v>-2.028818248</v>
       </c>
       <c r="P98">
-        <v>-8.002579456000001</v>
+        <v>-8.115272992000001</v>
       </c>
       <c r="Q98">
-        <v>-8.342579456000001</v>
+        <v>-8.455272992000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.587703384554887</v>
+        <v>3.43500451273985</v>
       </c>
       <c r="T98">
-        <v>39.3224369369147</v>
+        <v>52.42991591588628</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05205859071337213</v>
+        <v>0.0515219042111724</v>
       </c>
       <c r="W98">
-        <v>0.2235245843097869</v>
+        <v>0.2236511349870056</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2602929535668606</v>
+        <v>0.257609521055862</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.319991736319591</v>
+        <v>0.3218917363195909</v>
       </c>
       <c r="C99">
-        <v>-33.74670539003212</v>
+        <v>-34.49902157958959</v>
       </c>
       <c r="D99">
-        <v>22.51109460996788</v>
+        <v>22.35617842041041</v>
       </c>
       <c r="E99">
-        <v>53.9078</v>
+        <v>54.5052</v>
       </c>
       <c r="F99">
-        <v>57.9478</v>
+        <v>58.5452</v>
       </c>
       <c r="G99">
         <v>1.69</v>
@@ -9533,37 +9533,37 @@
         <v>3.52</v>
       </c>
       <c r="M99">
-        <v>13.66409124</v>
+        <v>13.80495816</v>
       </c>
       <c r="N99">
-        <v>-10.14409124</v>
+        <v>-10.28495816</v>
       </c>
       <c r="O99">
-        <v>-2.028818248</v>
+        <v>-2.056991632</v>
       </c>
       <c r="P99">
-        <v>-8.115272992000001</v>
+        <v>-8.227966528</v>
       </c>
       <c r="Q99">
-        <v>-8.455272992000001</v>
+        <v>-8.567966527999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.43500451273985</v>
+        <v>5.129606769109774</v>
       </c>
       <c r="T99">
-        <v>52.42991591588628</v>
+        <v>78.6448738738294</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0515219042111724</v>
+        <v>0.05099617049473187</v>
       </c>
       <c r="W99">
-        <v>0.2236511349870056</v>
+        <v>0.2237751029973422</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.257609521055862</v>
+        <v>0.2549808524736593</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3218917363195909</v>
+        <v>0.323791736319591</v>
       </c>
       <c r="C100">
-        <v>-34.49902157958959</v>
+        <v>-35.24922014677415</v>
       </c>
       <c r="D100">
-        <v>22.35617842041041</v>
+        <v>22.20337985322585</v>
       </c>
       <c r="E100">
-        <v>54.5052</v>
+        <v>55.1026</v>
       </c>
       <c r="F100">
-        <v>58.5452</v>
+        <v>59.1426</v>
       </c>
       <c r="G100">
         <v>1.69</v>
@@ -9615,37 +9615,37 @@
         <v>3.52</v>
       </c>
       <c r="M100">
-        <v>13.80495816</v>
+        <v>13.94582508</v>
       </c>
       <c r="N100">
-        <v>-10.28495816</v>
+        <v>-10.42582508</v>
       </c>
       <c r="O100">
-        <v>-2.056991632</v>
+        <v>-2.085165016</v>
       </c>
       <c r="P100">
-        <v>-8.227966528</v>
+        <v>-8.340660064000001</v>
       </c>
       <c r="Q100">
-        <v>-8.567966527999999</v>
+        <v>-8.680660064000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.129606769109774</v>
+        <v>10.21341353821955</v>
       </c>
       <c r="T100">
-        <v>78.6448738738294</v>
+        <v>157.2897477476588</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05099617049473187</v>
+        <v>0.05048105766145176</v>
       </c>
       <c r="W100">
-        <v>0.2237751029973422</v>
+        <v>0.2238965666034297</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2549808524736593</v>
+        <v>0.2524052883072587</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.323791736319591</v>
-      </c>
-      <c r="C101">
-        <v>-35.24922014677415</v>
-      </c>
-      <c r="D101">
-        <v>22.20337985322585</v>
-      </c>
-      <c r="E101">
-        <v>55.1026</v>
-      </c>
-      <c r="F101">
-        <v>59.1426</v>
-      </c>
-      <c r="G101">
-        <v>1.69</v>
-      </c>
-      <c r="H101">
-        <v>55.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.18</v>
-      </c>
-      <c r="K101">
-        <v>-0.3399999999999999</v>
-      </c>
-      <c r="L101">
-        <v>3.52</v>
-      </c>
-      <c r="M101">
-        <v>13.94582508</v>
-      </c>
-      <c r="N101">
-        <v>-10.42582508</v>
-      </c>
-      <c r="O101">
-        <v>-2.085165016</v>
-      </c>
-      <c r="P101">
-        <v>-8.340660064000001</v>
-      </c>
-      <c r="Q101">
-        <v>-8.680660064000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.21341353821955</v>
-      </c>
-      <c r="T101">
-        <v>157.2897477476588</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05048105766145176</v>
-      </c>
-      <c r="W101">
-        <v>0.2238965666034297</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2524052883072587</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
